--- a/artfynd/A 44517-2023 artfynd.xlsx
+++ b/artfynd/A 44517-2023 artfynd.xlsx
@@ -7193,7 +7193,7 @@
         <v>101775120</v>
       </c>
       <c r="B61" t="n">
-        <v>97439</v>
+        <v>97442</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 44517-2023 artfynd.xlsx
+++ b/artfynd/A 44517-2023 artfynd.xlsx
@@ -7193,7 +7193,7 @@
         <v>101775120</v>
       </c>
       <c r="B61" t="n">
-        <v>97442</v>
+        <v>97443</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 44517-2023 artfynd.xlsx
+++ b/artfynd/A 44517-2023 artfynd.xlsx
@@ -7193,7 +7193,7 @@
         <v>101775120</v>
       </c>
       <c r="B61" t="n">
-        <v>97443</v>
+        <v>97448</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 44517-2023 artfynd.xlsx
+++ b/artfynd/A 44517-2023 artfynd.xlsx
@@ -7193,7 +7193,7 @@
         <v>101775120</v>
       </c>
       <c r="B61" t="n">
-        <v>97448</v>
+        <v>97450</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 44517-2023 artfynd.xlsx
+++ b/artfynd/A 44517-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ67"/>
+  <dimension ref="A1:AZ72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135830027</v>
+        <v>137002851</v>
       </c>
       <c r="B5" t="n">
-        <v>83452</v>
+        <v>79557</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,37 +1027,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>308</v>
+        <v>283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sundsvalen, Jmt</t>
+          <t>Sundsvalen, Segerdalen, Kall, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>390620</v>
+        <v>390777</v>
       </c>
       <c r="R5" t="n">
-        <v>7061569</v>
+        <v>7061697</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,22 +1084,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>16:13</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>16:13</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,33 +1098,34 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Raul Vicente</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Raul Vicente</t>
+          <t>Raul Vicente, Ola Hammarström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135830027</t>
+          <t>https://artportalen.se/Sighting/137002851</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118378088</v>
+        <v>135830027</v>
       </c>
       <c r="B6" t="n">
-        <v>83302</v>
+        <v>83452</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,37 +1133,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Sundsvalen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>389534</v>
+        <v>390620</v>
       </c>
       <c r="R6" t="n">
-        <v>7061458</v>
+        <v>7061569</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,12 +1187,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1209,58 +1213,53 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Cajsa Björkén, Raul Vicente</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378088</t>
+          <t>https://artportalen.se/Sighting/135830027</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118378039</v>
+        <v>118378088</v>
       </c>
       <c r="B7" t="n">
-        <v>83298</v>
+        <v>83302</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>492</v>
+        <v>310</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>390411</v>
+        <v>389534</v>
       </c>
       <c r="R7" t="n">
-        <v>7061551</v>
+        <v>7061458</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1300,12 +1299,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1319,7 +1318,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>björkhögstubbe</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1336,58 +1335,54 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378039</t>
+          <t>https://artportalen.se/Sighting/118378088</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>101624404</v>
+        <v>118378039</v>
       </c>
       <c r="B8" t="n">
-        <v>96705</v>
+        <v>83298</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>535</v>
+        <v>492</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skuggmossa</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dicranodontium denudatum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brid.) E.Britton</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sundsvalen, ravin vid nordsidan., Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>389605</v>
+        <v>390411</v>
       </c>
       <c r="R8" t="n">
-        <v>7061466</v>
+        <v>7061551</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1411,12 +1406,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1425,44 +1420,38 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Bäckravin med granskog.</t>
-        </is>
-      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bergvägg.</t>
+          <t>björkhögstubbe</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Leif Appelgren, Fredrik Larsson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101624404</t>
+          <t>https://artportalen.se/Sighting/118378039</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103566149</v>
+        <v>137002813</v>
       </c>
       <c r="B9" t="n">
-        <v>81013</v>
+        <v>78835</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,34 +1459,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>735</v>
+        <v>498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skuggkraterlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gyalecta friesii</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Flot. ex Körb.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ravinskog i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalen, Segerdalen, Kall, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>390608</v>
+        <v>390677</v>
       </c>
       <c r="R9" t="n">
-        <v>7061565</v>
+        <v>7061698</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,12 +1516,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1538,73 +1530,93 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Rothåla gran</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Raul Vicente</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Maya Edlund, Rikard Anderberg, Martin Westberg, Robin Isaksson, Raul Vicente, Måns Svensson, Ola Hammarström</t>
+          <t>Raul Vicente, Ola Hammarström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566149</t>
+          <t>https://artportalen.se/Sighting/137002813</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103566189</v>
+        <v>101624404</v>
       </c>
       <c r="B10" t="n">
-        <v>81013</v>
+        <v>96705</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>735</v>
+        <v>535</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skuggkraterlav</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gyalecta friesii</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Flot. ex Körb.</t>
+          <t>(Brid.) E.Britton</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalen, ravin vid nordsidan., Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>389379</v>
+        <v>389605</v>
       </c>
       <c r="R10" t="n">
-        <v>7061454</v>
+        <v>7061466</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1631,12 +1643,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1645,35 +1657,41 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Bäckravin med granskog.</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Rothåla gran</t>
+          <t>Bergvägg.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
+          <t>Leif Appelgren, Fredrik Larsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566189</t>
+          <t>https://artportalen.se/Sighting/101624404</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118378021</v>
+        <v>103566149</v>
       </c>
       <c r="B11" t="n">
         <v>81013</v>
@@ -1704,17 +1722,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Ravinskog i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>389551</v>
+        <v>390608</v>
       </c>
       <c r="R11" t="n">
-        <v>7061475</v>
+        <v>7061565</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1757,30 +1775,30 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>granbas</t>
+          <t>Rothåla gran</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Maya Edlund, Rikard Anderberg, Martin Westberg, Robin Isaksson, Raul Vicente, Måns Svensson, Ola Hammarström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378021</t>
+          <t>https://artportalen.se/Sighting/103566149</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118378108</v>
+        <v>103566189</v>
       </c>
       <c r="B12" t="n">
         <v>81013</v>
@@ -1811,17 +1829,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>389432</v>
+        <v>389379</v>
       </c>
       <c r="R12" t="n">
-        <v>7061449</v>
+        <v>7061454</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1861,31 +1879,36 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Rothåla gran</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378108</t>
+          <t>https://artportalen.se/Sighting/103566189</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135830026</v>
+        <v>118378021</v>
       </c>
       <c r="B13" t="n">
-        <v>81158</v>
+        <v>81013</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,17 +1936,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sundsvalen, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>390620</v>
+        <v>389551</v>
       </c>
       <c r="R13" t="n">
-        <v>7061569</v>
+        <v>7061475</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1947,22 +1970,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>16:13</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>16:13</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1973,31 +1986,36 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>granbas</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Raul Vicente</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135830026</t>
+          <t>https://artportalen.se/Sighting/118378021</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135830028</v>
+        <v>118378108</v>
       </c>
       <c r="B14" t="n">
-        <v>81157</v>
+        <v>81013</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2025,17 +2043,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sundsvalen, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>390604</v>
+        <v>389432</v>
       </c>
       <c r="R14" t="n">
-        <v>7061567</v>
+        <v>7061449</v>
       </c>
       <c r="S14" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2059,22 +2077,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>16:15</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>16:15</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2089,27 +2097,27 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Raul Vicente</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135830028</t>
+          <t>https://artportalen.se/Sighting/118378108</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>102571913</v>
+        <v>135830026</v>
       </c>
       <c r="B15" t="n">
-        <v>92721</v>
+        <v>81158</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2117,40 +2125,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>918</v>
+        <v>735</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Skuggkraterlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Gyalecta friesii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>Flot. ex Körb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sundsvalen N, Nynäsbäcken O, Jmt</t>
+          <t>Sundsvalen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>389580</v>
+        <v>390620</v>
       </c>
       <c r="R15" t="n">
-        <v>7061470</v>
+        <v>7061569</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2174,12 +2179,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2188,92 +2203,71 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Rikard Anderberg, Maya Edlund, Raul Vicente, Ola Hammarström, Martin Westberg, Robin Isaksson</t>
+          <t>Cajsa Björkén, Raul Vicente</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102571913</t>
+          <t>https://artportalen.se/Sighting/135830026</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>103566174</v>
+        <v>135830028</v>
       </c>
       <c r="B16" t="n">
-        <v>81312</v>
+        <v>81157</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1049</v>
+        <v>735</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Skuggkraterlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Gyalecta friesii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Flot. ex Körb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>389653</v>
+        <v>390604</v>
       </c>
       <c r="R16" t="n">
-        <v>7061468</v>
+        <v>7061567</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2297,12 +2291,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2313,74 +2317,72 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Ved i rothåla , rönn?</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
+          <t>Cajsa Björkén, Raul Vicente</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566174</t>
+          <t>https://artportalen.se/Sighting/135830028</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>103566182</v>
+        <v>102571913</v>
       </c>
       <c r="B17" t="n">
-        <v>81312</v>
+        <v>92721</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1049</v>
+        <v>918</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalen N, Nynäsbäcken O, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>389508</v>
+        <v>389580</v>
       </c>
       <c r="R17" t="n">
-        <v>7061484</v>
+        <v>7061470</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2404,12 +2406,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2418,38 +2420,54 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Rothåla gran</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
+          <t>Rikard Anderberg, Maya Edlund, Raul Vicente, Ola Hammarström, Martin Westberg, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566182</t>
+          <t>https://artportalen.se/Sighting/102571913</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>102911996</v>
+        <v>103566174</v>
       </c>
       <c r="B18" t="n">
-        <v>91905</v>
+        <v>81312</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2457,40 +2475,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>1049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sundsvalen, Jmt</t>
+          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>389598</v>
+        <v>389653</v>
       </c>
       <c r="R18" t="n">
-        <v>7061433</v>
+        <v>7061468</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2514,12 +2529,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2528,75 +2543,76 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Ved i rothåla , rönn?</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Robin Isaksson</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Martin Westberg, Raul Vicente, Måns Svensson, Maya Edlund, Ola Hammarström</t>
+          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102911996</t>
+          <t>https://artportalen.se/Sighting/103566174</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>102911954</v>
+        <v>103566182</v>
       </c>
       <c r="B19" t="n">
-        <v>91923</v>
+        <v>81312</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1204</v>
+        <v>1049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sundsvalen, Jmt</t>
+          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>390406</v>
+        <v>389508</v>
       </c>
       <c r="R19" t="n">
-        <v>7061546</v>
+        <v>7061484</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2620,12 +2636,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2634,69 +2650,76 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Rothåla gran</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Robin Isaksson</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Maya Edlund, Rikard Anderberg, Måns Svensson, Raul Vicente, Martin Westberg, Robin Isaksson</t>
+          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102911954</t>
+          <t>https://artportalen.se/Sighting/103566182</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118378107</v>
+        <v>102911996</v>
       </c>
       <c r="B20" t="n">
-        <v>91923</v>
+        <v>91905</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Sundsvalen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>389435</v>
+        <v>389598</v>
       </c>
       <c r="R20" t="n">
-        <v>7061405</v>
+        <v>7061433</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2723,12 +2746,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2737,38 +2760,34 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Robin Isaksson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Robin Isaksson, Martin Westberg, Raul Vicente, Måns Svensson, Maya Edlund, Ola Hammarström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378107</t>
+          <t>https://artportalen.se/Sighting/102911996</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>102571916</v>
+        <v>102911954</v>
       </c>
       <c r="B21" t="n">
-        <v>79486</v>
+        <v>91923</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2776,21 +2795,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1249</v>
+        <v>1204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2799,14 +2818,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sundsvalen N, Nynäsbäcken O, Jmt</t>
+          <t>Sundsvalen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>389580</v>
+        <v>390406</v>
       </c>
       <c r="R21" t="n">
-        <v>7061470</v>
+        <v>7061546</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2851,50 +2870,30 @@
       <c r="AG21" t="b">
         <v>0</v>
       </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Robin Isaksson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Rikard Anderberg, Maya Edlund, Raul Vicente, Ola Hammarström, Martin Westberg, Robin Isaksson</t>
+          <t>Ola Hammarström, Maya Edlund, Rikard Anderberg, Måns Svensson, Raul Vicente, Martin Westberg, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102571916</t>
+          <t>https://artportalen.se/Sighting/102911954</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>103566191</v>
+        <v>118378107</v>
       </c>
       <c r="B22" t="n">
-        <v>79486</v>
+        <v>91923</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2902,37 +2901,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1249</v>
+        <v>1204</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>389472</v>
+        <v>389435</v>
       </c>
       <c r="R22" t="n">
-        <v>7061433</v>
+        <v>7061405</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2975,33 +2974,33 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566191</t>
+          <t>https://artportalen.se/Sighting/118378107</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118378032</v>
+        <v>102571916</v>
       </c>
       <c r="B23" t="n">
-        <v>75413</v>
+        <v>79486</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3009,34 +3008,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1461</v>
+        <v>1249</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brun skärelav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Schismatomma umbrinum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Coppins &amp; P.James) P.M.Jørg. &amp; Tønsberg</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Sundsvalen N, Nynäsbäcken O, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>390053</v>
+        <v>389580</v>
       </c>
       <c r="R23" t="n">
-        <v>7061464</v>
+        <v>7061470</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3077,38 +3079,54 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>lodyta</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Rikard Anderberg, Maya Edlund, Raul Vicente, Ola Hammarström, Martin Westberg, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378032</t>
+          <t>https://artportalen.se/Sighting/102571916</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118378085</v>
+        <v>103566191</v>
       </c>
       <c r="B24" t="n">
-        <v>75413</v>
+        <v>79486</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3116,37 +3134,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1461</v>
+        <v>1249</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brun skärelav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Schismatomma umbrinum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Coppins &amp; P.James) P.M.Jørg. &amp; Tønsberg</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>389631</v>
+        <v>389472</v>
       </c>
       <c r="R24" t="n">
-        <v>7061464</v>
+        <v>7061433</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3189,76 +3207,71 @@
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>lodyta</t>
-        </is>
-      </c>
-      <c r="AP24" t="inlineStr">
-        <is>
-          <t>Uppsala-Evolutionsmuseet</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378085</t>
+          <t>https://artportalen.se/Sighting/103566191</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>103566181</v>
+        <v>118378032</v>
       </c>
       <c r="B25" t="n">
-        <v>83312</v>
+        <v>75413</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1467</v>
+        <v>1461</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Brun skärelav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Schismatomma umbrinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Coppins &amp; P.James) P.M.Jørg. &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>389508</v>
+        <v>390053</v>
       </c>
       <c r="R25" t="n">
-        <v>7061484</v>
+        <v>7061464</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3282,12 +3295,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3301,71 +3314,71 @@
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Rothåla gran</t>
+          <t>lodyta</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566181</t>
+          <t>https://artportalen.se/Sighting/118378032</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>103566194</v>
+        <v>118378085</v>
       </c>
       <c r="B26" t="n">
-        <v>83312</v>
+        <v>75413</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1467</v>
+        <v>1461</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Brun skärelav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Schismatomma umbrinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Coppins &amp; P.James) P.M.Jørg. &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>389472</v>
+        <v>389631</v>
       </c>
       <c r="R26" t="n">
-        <v>7061433</v>
+        <v>7061464</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3408,30 +3421,35 @@
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>lodyta</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>Uppsala-Evolutionsmuseet</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566194</t>
+          <t>https://artportalen.se/Sighting/118378085</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118378034</v>
+        <v>103566181</v>
       </c>
       <c r="B27" t="n">
         <v>83312</v>
@@ -3462,17 +3480,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>390082</v>
+        <v>389508</v>
       </c>
       <c r="R27" t="n">
-        <v>7061482</v>
+        <v>7061484</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3496,12 +3514,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3515,33 +3533,33 @@
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>granbas</t>
+          <t>Rothåla gran</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378034</t>
+          <t>https://artportalen.se/Sighting/103566181</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135830030</v>
+        <v>103566194</v>
       </c>
       <c r="B28" t="n">
-        <v>83465</v>
+        <v>83312</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3569,17 +3587,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sundsvalen, Jmt</t>
+          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>390604</v>
+        <v>389472</v>
       </c>
       <c r="R28" t="n">
-        <v>7061561</v>
+        <v>7061433</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3603,22 +3621,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>16:32</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>16:32</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3629,69 +3637,74 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Raul Vicente</t>
+          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135830030</t>
+          <t>https://artportalen.se/Sighting/103566194</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>103566148</v>
+        <v>118378034</v>
       </c>
       <c r="B29" t="n">
-        <v>83315</v>
+        <v>83312</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Liten blekspik</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sclerophora peronella</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ravinskog i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>390101</v>
+        <v>390082</v>
       </c>
       <c r="R29" t="n">
         <v>7061482</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3734,71 +3747,71 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Björkhögstubbe</t>
+          <t>granbas</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Maya Edlund, Rikard Anderberg, Martin Westberg, Robin Isaksson, Raul Vicente, Måns Svensson, Ola Hammarström</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566148</t>
+          <t>https://artportalen.se/Sighting/118378034</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>103566176</v>
+        <v>135830030</v>
       </c>
       <c r="B30" t="n">
-        <v>83315</v>
+        <v>83465</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Liten blekspik</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sclerophora peronella</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>389653</v>
+        <v>390604</v>
       </c>
       <c r="R30" t="n">
-        <v>7061468</v>
+        <v>7061561</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3822,12 +3835,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3838,33 +3861,28 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Rönn</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
+          <t>Cajsa Björkén, Raul Vicente</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566176</t>
+          <t>https://artportalen.se/Sighting/135830030</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>115808940</v>
+        <v>103566148</v>
       </c>
       <c r="B31" t="n">
         <v>83315</v>
@@ -3893,19 +3911,16 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sundsvalens nordsluttning, Jmt</t>
+          <t>Ravinskog i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>389685</v>
+        <v>390101</v>
       </c>
       <c r="R31" t="n">
-        <v>7061500</v>
+        <v>7061482</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3932,17 +3947,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3951,36 +3961,35 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
-      <c r="AP31" t="inlineStr">
-        <is>
-          <t>Uppsala-Evolutionsmuseet</t>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Björkhögstubbe</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Maya Edlund, Rikard Anderberg, Martin Westberg, Robin Isaksson, Raul Vicente, Måns Svensson, Ola Hammarström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115808940</t>
+          <t>https://artportalen.se/Sighting/103566148</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118378042</v>
+        <v>103566176</v>
       </c>
       <c r="B32" t="n">
         <v>83315</v>
@@ -4011,17 +4020,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>390411</v>
+        <v>389653</v>
       </c>
       <c r="R32" t="n">
-        <v>7061551</v>
+        <v>7061468</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4045,12 +4054,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4064,33 +4073,33 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>björkhögstubbe</t>
+          <t>Rönn</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378042</t>
+          <t>https://artportalen.se/Sighting/103566176</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>102911949</v>
+        <v>115808940</v>
       </c>
       <c r="B33" t="n">
-        <v>75421</v>
+        <v>83315</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4098,21 +4107,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1776</v>
+        <v>1469</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Liten blekspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Sclerophora peronella</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4121,17 +4130,17 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sundsvalen, Jmt</t>
+          <t>Sundsvalens nordsluttning, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>390406</v>
+        <v>389685</v>
       </c>
       <c r="R33" t="n">
-        <v>7061546</v>
+        <v>7061500</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4155,12 +4164,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4173,45 +4187,35 @@
       <c r="AG33" t="b">
         <v>0</v>
       </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>Uppsala-Evolutionsmuseet</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Robin Isaksson</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Maya Edlund, Rikard Anderberg, Måns Svensson, Raul Vicente, Martin Westberg, Robin Isaksson</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102911949</t>
+          <t>https://artportalen.se/Sighting/115808940</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>103566178</v>
+        <v>118378042</v>
       </c>
       <c r="B34" t="n">
-        <v>75421</v>
+        <v>83315</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4219,37 +4223,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1776</v>
+        <v>1469</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Liten blekspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Sclerophora peronella</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>389508</v>
+        <v>390411</v>
       </c>
       <c r="R34" t="n">
-        <v>7061484</v>
+        <v>7061551</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4273,12 +4277,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4292,30 +4296,30 @@
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Grangren</t>
+          <t>björkhögstubbe</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566178</t>
+          <t>https://artportalen.se/Sighting/118378042</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>106652352</v>
+        <v>102911949</v>
       </c>
       <c r="B35" t="n">
         <v>75421</v>
@@ -4349,14 +4353,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sundsvalen, Jormlien, Frostviken, Jmt</t>
+          <t>Sundsvalen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>389539</v>
+        <v>390406</v>
       </c>
       <c r="R35" t="n">
-        <v>7061476</v>
+        <v>7061546</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4383,12 +4387,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4397,40 +4401,46 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Oceanisk grannaturskog.</t>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Raul Vicente</t>
+          <t>Robin Isaksson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Raul Vicente</t>
+          <t>Ola Hammarström, Maya Edlund, Rikard Anderberg, Måns Svensson, Raul Vicente, Martin Westberg, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106652352</t>
+          <t>https://artportalen.se/Sighting/102911949</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118378020</v>
+        <v>103566178</v>
       </c>
       <c r="B36" t="n">
         <v>75421</v>
@@ -4461,17 +4471,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>389551</v>
+        <v>389508</v>
       </c>
       <c r="R36" t="n">
-        <v>7061475</v>
+        <v>7061484</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4495,12 +4505,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4514,68 +4524,71 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>granbas</t>
+          <t>Grangren</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378020</t>
+          <t>https://artportalen.se/Sighting/103566178</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118378115</v>
+        <v>106652352</v>
       </c>
       <c r="B37" t="n">
-        <v>80433</v>
+        <v>75421</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>1776</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Sundsvalen, Jormlien, Frostviken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>389580</v>
+        <v>389539</v>
       </c>
       <c r="R37" t="n">
-        <v>7061470</v>
+        <v>7061476</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4616,76 +4629,81 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>rönn</t>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Oceanisk grannaturskog.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Raul Vicente</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Raul Vicente</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378115</t>
+          <t>https://artportalen.se/Sighting/106652352</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135830025</v>
+        <v>118378020</v>
       </c>
       <c r="B38" t="n">
-        <v>98000</v>
+        <v>75421</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2389</v>
+        <v>1776</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Purpurmylia</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Mylia taylorii</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hook.) Gray</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sundsvalen, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>390836</v>
+        <v>389551</v>
       </c>
       <c r="R38" t="n">
-        <v>7061634</v>
+        <v>7061475</v>
       </c>
       <c r="S38" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4709,22 +4727,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>16:08</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>16:08</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4735,74 +4743,71 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>granbas</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Raul Vicente</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135830025</t>
+          <t>https://artportalen.se/Sighting/118378020</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>102583100</v>
+        <v>118378115</v>
       </c>
       <c r="B39" t="n">
-        <v>96350</v>
+        <v>80433</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2813</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>utan kapsel</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sundsvalen N, O Nynäsbäcken, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>389560</v>
+        <v>389580</v>
       </c>
       <c r="R39" t="n">
-        <v>7061465</v>
+        <v>7061470</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4829,12 +4834,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4843,44 +4848,38 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>ravin</t>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Rikard Anderberg, Maya Edlund</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102583100</t>
+          <t>https://artportalen.se/Sighting/118378115</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>101624453</v>
+        <v>135830025</v>
       </c>
       <c r="B40" t="n">
-        <v>96459</v>
+        <v>98000</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4888,41 +4887,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2819</v>
+        <v>2389</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Trind spretmossa</t>
+          <t>Purpurmylia</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Herzogiella striatella</t>
+          <t>Mylia taylorii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hook.) Gray</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sundsvalen, ravin vid nordsidan., Jmt</t>
+          <t>Sundsvalen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>389605</v>
+        <v>390836</v>
       </c>
       <c r="R40" t="n">
-        <v>7061466</v>
+        <v>7061634</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4946,12 +4941,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4960,44 +4965,33 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>Bäckravin med granskog.</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Bergvägg.</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Leif Appelgren, Fredrik Larsson</t>
+          <t>Cajsa Björkén, Raul Vicente</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101624453</t>
+          <t>https://artportalen.se/Sighting/135830025</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>101775139</v>
+        <v>102583100</v>
       </c>
       <c r="B41" t="n">
-        <v>96459</v>
+        <v>96350</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5005,34 +4999,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2819</v>
+        <v>2813</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trind spretmossa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Herzogiella striatella</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>utan kapsel</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sundsvalen, norra sluttningen, Jmt</t>
+          <t>Sundsvalen N, O Nynäsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>389642</v>
+        <v>389560</v>
       </c>
       <c r="R41" t="n">
-        <v>7061462</v>
+        <v>7061465</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5059,17 +5061,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Projektet Northern hepatic mat</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5078,71 +5075,86 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>ravin</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Tomas Hallingbäck</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Tomas Hallingbäck, Fredrik Larsson, Karin Wiklund, Leif Appelgren, Anna Pielach</t>
+          <t>Rikard Anderberg, Maya Edlund</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101775139</t>
+          <t>https://artportalen.se/Sighting/102583100</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118378106</v>
+        <v>101624453</v>
       </c>
       <c r="B42" t="n">
-        <v>79327</v>
+        <v>96459</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>2819</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trind spretmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Herzogiella striatella</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Sundsvalen, ravin vid nordsidan., Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>389412</v>
+        <v>389605</v>
       </c>
       <c r="R42" t="n">
-        <v>7061456</v>
+        <v>7061466</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5166,12 +5178,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5180,38 +5192,44 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Bäckravin med granskog.</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>Bergvägg.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Leif Appelgren, Fredrik Larsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378106</t>
+          <t>https://artportalen.se/Sighting/101624453</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>103566195</v>
+        <v>101775139</v>
       </c>
       <c r="B43" t="n">
-        <v>75300</v>
+        <v>96459</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5219,37 +5237,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6428</v>
+        <v>2819</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Trind spretmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Herzogiella striatella</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalen, norra sluttningen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>389472</v>
+        <v>389642</v>
       </c>
       <c r="R43" t="n">
-        <v>7061433</v>
+        <v>7061462</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5273,12 +5291,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Projektet Northern hepatic mat</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5289,58 +5312,53 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Tomas Hallingbäck</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
+          <t>Tomas Hallingbäck, Fredrik Larsson, Karin Wiklund, Leif Appelgren, Anna Pielach</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566195</t>
+          <t>https://artportalen.se/Sighting/101775139</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118378022</v>
+        <v>118378106</v>
       </c>
       <c r="B44" t="n">
-        <v>75300</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5350,10 +5368,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>389551</v>
+        <v>389412</v>
       </c>
       <c r="R44" t="n">
-        <v>7061475</v>
+        <v>7061456</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5380,12 +5398,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5399,7 +5417,7 @@
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>granbas</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5416,16 +5434,16 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378022</t>
+          <t>https://artportalen.se/Sighting/118378106</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>103566197</v>
+        <v>103566195</v>
       </c>
       <c r="B45" t="n">
-        <v>83290</v>
+        <v>75300</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5433,21 +5451,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6439</v>
+        <v>6428</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5523,16 +5541,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566197</t>
+          <t>https://artportalen.se/Sighting/103566195</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118378040</v>
+        <v>118378022</v>
       </c>
       <c r="B46" t="n">
-        <v>83290</v>
+        <v>75300</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5540,21 +5558,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6439</v>
+        <v>6428</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5564,10 +5582,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>390411</v>
+        <v>389551</v>
       </c>
       <c r="R46" t="n">
-        <v>7061551</v>
+        <v>7061475</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5613,7 +5631,7 @@
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>björkhögstubbe</t>
+          <t>granbas</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5630,54 +5648,54 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378040</t>
+          <t>https://artportalen.se/Sighting/118378022</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118378027</v>
+        <v>103566197</v>
       </c>
       <c r="B47" t="n">
-        <v>83307</v>
+        <v>83290</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6440</v>
+        <v>6439</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>389582</v>
+        <v>389472</v>
       </c>
       <c r="R47" t="n">
-        <v>7061446</v>
+        <v>7061433</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5701,17 +5719,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5725,55 +5738,55 @@
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378027</t>
+          <t>https://artportalen.se/Sighting/103566197</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118378086</v>
+        <v>118378040</v>
       </c>
       <c r="B48" t="n">
-        <v>79413</v>
+        <v>83290</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6450</v>
+        <v>6439</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5783,10 +5796,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>389615</v>
+        <v>390411</v>
       </c>
       <c r="R48" t="n">
-        <v>7061456</v>
+        <v>7061551</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5813,12 +5826,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5832,7 +5845,7 @@
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>björkhögstubbe</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5849,16 +5862,16 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378086</t>
+          <t>https://artportalen.se/Sighting/118378040</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118378113</v>
+        <v>118378027</v>
       </c>
       <c r="B49" t="n">
-        <v>80432</v>
+        <v>83307</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5866,21 +5879,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5890,10 +5903,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>389580</v>
+        <v>389582</v>
       </c>
       <c r="R49" t="n">
-        <v>7061470</v>
+        <v>7061446</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5920,12 +5933,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5939,7 +5957,7 @@
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -5956,54 +5974,57 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378113</t>
+          <t>https://artportalen.se/Sighting/118378027</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135830023</v>
+        <v>137002816</v>
       </c>
       <c r="B50" t="n">
-        <v>79729</v>
+        <v>83463</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6459</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sundsvalen, Jmt</t>
+          <t>Sundsvalen, Segerdalen, Kall, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>390836</v>
+        <v>390677</v>
       </c>
       <c r="R50" t="n">
-        <v>7061634</v>
+        <v>7061698</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6027,22 +6048,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6051,71 +6062,89 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Raul Vicente</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Raul Vicente</t>
+          <t>Raul Vicente, Ola Hammarström</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135830023</t>
+          <t>https://artportalen.se/Sighting/137002816</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>103432381</v>
+        <v>118378086</v>
       </c>
       <c r="B51" t="n">
-        <v>80461</v>
+        <v>79413</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6462</v>
+        <v>6450</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sundsvalen, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>390528</v>
+        <v>389615</v>
       </c>
       <c r="R51" t="n">
-        <v>7061549</v>
+        <v>7061456</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6142,12 +6171,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2022-07-24</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2022-07-24</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6156,60 +6185,60 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>block</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Robin Isaksson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Martin Westberg</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103432381</t>
+          <t>https://artportalen.se/Sighting/118378086</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118378112</v>
+        <v>118378113</v>
       </c>
       <c r="B52" t="n">
-        <v>80468</v>
+        <v>80432</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6285,54 +6314,54 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378112</t>
+          <t>https://artportalen.se/Sighting/118378113</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>103566180</v>
+        <v>135830023</v>
       </c>
       <c r="B53" t="n">
-        <v>83305</v>
+        <v>79729</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6486</v>
+        <v>6459</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>389508</v>
+        <v>390836</v>
       </c>
       <c r="R53" t="n">
-        <v>7061484</v>
+        <v>7061634</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6356,12 +6385,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6372,71 +6411,69 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Rothåla gran</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
+          <t>Cajsa Björkén, Raul Vicente</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566180</t>
+          <t>https://artportalen.se/Sighting/135830023</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118378024</v>
+        <v>103432381</v>
       </c>
       <c r="B54" t="n">
-        <v>83305</v>
+        <v>80461</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6486</v>
+        <v>6462</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Sundsvalen, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>389551</v>
+        <v>390528</v>
       </c>
       <c r="R54" t="n">
-        <v>7061475</v>
+        <v>7061549</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6463,12 +6500,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-24</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-24</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6477,60 +6514,60 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>granbas</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Robin Isaksson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Robin Isaksson, Martin Westberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378024</t>
+          <t>https://artportalen.se/Sighting/103432381</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118378045</v>
+        <v>118378112</v>
       </c>
       <c r="B55" t="n">
-        <v>78333</v>
+        <v>80468</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228575</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Brun svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenothecopsis epithallina</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6540,10 +6577,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>390743</v>
+        <v>389580</v>
       </c>
       <c r="R55" t="n">
-        <v>7061546</v>
+        <v>7061470</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6570,12 +6607,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6589,12 +6626,7 @@
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>på Chaenotheca på grov gran</t>
-        </is>
-      </c>
-      <c r="AP55" t="inlineStr">
-        <is>
-          <t>Uppsala-Evolutionsmuseet</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6611,38 +6643,38 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378045</t>
+          <t>https://artportalen.se/Sighting/118378112</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>103566184</v>
+        <v>103566180</v>
       </c>
       <c r="B56" t="n">
-        <v>78339</v>
+        <v>83305</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228579</v>
+        <v>6486</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6701,7 +6733,7 @@
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Rothåla gran</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -6718,38 +6750,38 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566184</t>
+          <t>https://artportalen.se/Sighting/103566180</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118378028</v>
+        <v>118378024</v>
       </c>
       <c r="B57" t="n">
-        <v>78339</v>
+        <v>83305</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228579</v>
+        <v>6486</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6759,10 +6791,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>389582</v>
+        <v>389551</v>
       </c>
       <c r="R57" t="n">
-        <v>7061446</v>
+        <v>7061475</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6797,11 +6829,6 @@
           <t>2022-07-27</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6813,7 +6840,7 @@
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>granbas</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -6830,33 +6857,38 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378028</t>
+          <t>https://artportalen.se/Sighting/118378024</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>103432374</v>
+        <v>137002846</v>
       </c>
       <c r="B58" t="n">
-        <v>86637</v>
+        <v>83461</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229848</v>
+        <v>6486</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Skuggnål</t>
+        </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Refractohilum galligenum</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>D.Hawksw.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6865,14 +6897,14 @@
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sundsvalen, Jmt</t>
+          <t>Sundsvalen, Segerdalen, Kall, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>390528</v>
+        <v>390777</v>
       </c>
       <c r="R58" t="n">
-        <v>7061549</v>
+        <v>7061697</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6899,12 +6931,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2022-07-24</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2022-07-24</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6913,93 +6945,69 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>stuplav</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="AL58" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Nephroma bellum # rönn</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Robin Isaksson</t>
+          <t>Raul Vicente</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Martin Westberg</t>
+          <t>Raul Vicente, Ola Hammarström</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103432374</t>
+          <t>https://artportalen.se/Sighting/137002846</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>101775142</v>
+        <v>118378045</v>
       </c>
       <c r="B59" t="n">
-        <v>97921</v>
+        <v>78333</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>233219</v>
+        <v>228575</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vågig rutlungmossa</t>
+          <t>Brun svartspik</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Conocephalum salebrosum</t>
+          <t>Chaenothecopsis epithallina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Szweyk., Buczk. &amp; Odrzyk.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sundsvalen, norra sluttningen, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>390389</v>
+        <v>390743</v>
       </c>
       <c r="R59" t="n">
-        <v>7061515</v>
+        <v>7061546</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7026,17 +7034,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Projektet Northern hepatic mat</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7047,73 +7050,79 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>på Chaenotheca på grov gran</t>
+        </is>
+      </c>
+      <c r="AP59" t="inlineStr">
+        <is>
+          <t>Uppsala-Evolutionsmuseet</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Tomas Hallingbäck</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Tomas Hallingbäck, Fredrik Larsson, Karin Wiklund, Leif Appelgren, Anna Pielach</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101775142</t>
+          <t>https://artportalen.se/Sighting/118378045</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>102583094</v>
+        <v>103566184</v>
       </c>
       <c r="B60" t="n">
-        <v>97921</v>
+        <v>78339</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>233219</v>
+        <v>228579</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vågig rutlungmossa</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Conocephalum salebrosum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Szweyk., Buczk. &amp; Odrzyk.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sundsvalen N, O Nynäsbäcken, Jmt</t>
+          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>389560</v>
+        <v>389508</v>
       </c>
       <c r="R60" t="n">
-        <v>7061465</v>
+        <v>7061484</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7137,12 +7146,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7151,84 +7160,73 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>ravin</t>
-        </is>
-      </c>
-      <c r="AQ60" t="inlineStr">
-        <is>
-          <t>Rikard Anderberg</t>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Rikard Anderberg, Maya Edlund</t>
+          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102583094</t>
+          <t>https://artportalen.se/Sighting/103566184</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>101775120</v>
+        <v>118378028</v>
       </c>
       <c r="B61" t="n">
-        <v>97450</v>
+        <v>78339</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>233357</v>
+        <v>228579</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lidvitmossa</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sphagnum rubiginosum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Flatberg</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sundsvalen, norra sluttningen, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>390757</v>
+        <v>389582</v>
       </c>
       <c r="R61" t="n">
-        <v>7061536</v>
+        <v>7061446</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7255,17 +7253,17 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Projektet Northern hepatic mat</t>
+          <t>mikroskoperad</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7276,80 +7274,77 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Tomas Hallingbäck</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Tomas Hallingbäck, Fredrik Larsson, Karin Wiklund, Leif Appelgren, Anna Pielach</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101775120</t>
+          <t>https://artportalen.se/Sighting/118378028</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>102650188</v>
+        <v>137002814</v>
       </c>
       <c r="B62" t="n">
-        <v>80474</v>
+        <v>78485</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>264143</v>
+        <v>228579</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Brittisk torsklav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Peltigera britannica</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Gyeln.) Holt.-Hartw. &amp; Tønsberg</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sundsvalen, Jmt</t>
+          <t>Sundsvalen, Segerdalen, Kall, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>389672</v>
+        <v>390677</v>
       </c>
       <c r="R62" t="n">
-        <v>7061478</v>
+        <v>7061698</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7373,17 +7368,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Andra moderna lokalen för Sverige.</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7398,12 +7388,22 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Granskog i ravin.</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Nordvänd skuggig, fuktig lodyta.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7414,56 +7414,43 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Raul Vicente, Måns Svensson, Ola Hammarström, Robin Isaksson, Martin Westberg, Rikard Anderberg, Maya Edlund</t>
+          <t>Raul Vicente, Ola Hammarström</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102650188</t>
+          <t>https://artportalen.se/Sighting/137002814</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>102650204</v>
+        <v>103432374</v>
       </c>
       <c r="B63" t="n">
-        <v>80474</v>
+        <v>86637</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>264143</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Brittisk torsklav</t>
-        </is>
+        <v>229848</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Peltigera britannica</t>
+          <t>Refractohilum galligenum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Holt.-Hartw. &amp; Tønsberg</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
@@ -7472,10 +7459,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>389623</v>
+        <v>390528</v>
       </c>
       <c r="R63" t="n">
-        <v>7061457</v>
+        <v>7061549</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7502,17 +7489,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-24</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Andra moderna lokalen i Sverige. Dellokal 2 i Sundsvalen. Arten är även känd från Skäckerfjällen. Västlig och oceanisk art som endast var känd från Västergötland, första halvan av 1900-talet.</t>
+          <t>2022-07-24</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7521,85 +7503,96 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>Granskog i ravin.</t>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>stuplav</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="AL63" t="inlineStr">
+        <is>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Nordvänd skuggig, fuktig lodyta.</t>
+          <t>Nephroma bellum # rönn</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Raul Vicente</t>
+          <t>Robin Isaksson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Raul Vicente, Måns Svensson, Ola Hammarström, Robin Isaksson, Martin Westberg, Rikard Anderberg, Maya Edlund</t>
+          <t>Robin Isaksson, Martin Westberg</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102650204</t>
+          <t>https://artportalen.se/Sighting/103432374</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135830031</v>
+        <v>101775142</v>
       </c>
       <c r="B64" t="n">
-        <v>80606</v>
+        <v>97921</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>264143</v>
+        <v>233219</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Brittisk torsklav</t>
+          <t>Vågig rutlungmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Peltigera britannica</t>
+          <t>Conocephalum salebrosum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Holt.-Hartw. &amp; Tønsberg</t>
+          <t>Szweyk., Buczk. &amp; Odrzyk.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sundsvalen, Jmt</t>
+          <t>Sundsvalen, norra sluttningen, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>389640</v>
+        <v>390389</v>
       </c>
       <c r="R64" t="n">
-        <v>7061467</v>
+        <v>7061515</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7623,27 +7616,17 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>17:16</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>17:16</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Återfynd på känd lokal</t>
+          <t>Projektet Northern hepatic mat</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7652,67 +7635,72 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Tomas Hallingbäck</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Raul Vicente</t>
+          <t>Tomas Hallingbäck, Fredrik Larsson, Karin Wiklund, Leif Appelgren, Anna Pielach</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135830031</t>
+          <t>https://artportalen.se/Sighting/101775142</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>102911994</v>
+        <v>102583094</v>
       </c>
       <c r="B65" t="n">
-        <v>79497</v>
+        <v>97921</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6000492</v>
+        <v>233219</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Vågig rutlungmossa</t>
+        </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Protoparmelia ochrococca</t>
+          <t>Conocephalum salebrosum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) P.M.Jørg. et al.</t>
+          <t>Szweyk., Buczk. &amp; Odrzyk.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Sundsvalen, Jmt</t>
+          <t>Sundsvalen N, O Nynäsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>389598</v>
+        <v>389560</v>
       </c>
       <c r="R65" t="n">
-        <v>7061433</v>
+        <v>7061465</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7757,78 +7745,83 @@
       <c r="AG65" t="b">
         <v>0</v>
       </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>ravin</t>
+        </is>
+      </c>
+      <c r="AQ65" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Robin Isaksson</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Martin Westberg, Raul Vicente, Måns Svensson, Rikard Anderberg, Maya Edlund, Ola Hammarström</t>
+          <t>Rikard Anderberg, Maya Edlund</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102911994</t>
+          <t>https://artportalen.se/Sighting/102583094</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>103566147</v>
+        <v>101775120</v>
       </c>
       <c r="B66" t="n">
-        <v>79497</v>
+        <v>97450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6000492</v>
+        <v>233357</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Lidvitmossa</t>
+        </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Protoparmelia ochrococca</t>
+          <t>Sphagnum rubiginosum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) P.M.Jørg. et al.</t>
+          <t>Flatberg</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Ravinskog i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalen, norra sluttningen, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>390019</v>
+        <v>390757</v>
       </c>
       <c r="R66" t="n">
-        <v>7061472</v>
+        <v>7061536</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7852,12 +7845,17 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Projektet Northern hepatic mat</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7868,66 +7866,77 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Tomas Hallingbäck</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Maya Edlund, Rikard Anderberg, Martin Westberg, Robin Isaksson, Raul Vicente, Måns Svensson, Ola Hammarström</t>
+          <t>Tomas Hallingbäck, Fredrik Larsson, Karin Wiklund, Leif Appelgren, Anna Pielach</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566147</t>
+          <t>https://artportalen.se/Sighting/101775120</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118378110</v>
+        <v>102650188</v>
       </c>
       <c r="B67" t="n">
-        <v>79497</v>
+        <v>80474</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6000492</v>
+        <v>264143</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Brittisk torsklav</t>
+        </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Protoparmelia ochrococca</t>
+          <t>Peltigera britannica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) P.M.Jørg. et al.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Gyeln.) Holt.-Hartw. &amp; Tønsberg</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Sundsvalen, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>389580</v>
+        <v>389672</v>
       </c>
       <c r="R67" t="n">
-        <v>7061470</v>
+        <v>7061478</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7954,12 +7963,17 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Andra moderna lokalen för Sverige.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7968,27 +7982,603 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Granskog i ravin.</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>Nordvänd skuggig, fuktig lodyta.</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Raul Vicente</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Raul Vicente, Måns Svensson, Ola Hammarström, Robin Isaksson, Martin Westberg, Rikard Anderberg, Maya Edlund</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102650188</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>102650204</v>
+      </c>
+      <c r="B68" t="n">
+        <v>80474</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>264143</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Brittisk torsklav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Peltigera britannica</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Holt.-Hartw. &amp; Tønsberg</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Sundsvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>389623</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7061457</v>
+      </c>
+      <c r="S68" t="n">
+        <v>25</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Andra moderna lokalen i Sverige. Dellokal 2 i Sundsvalen. Arten är även känd från Skäckerfjällen. Västlig och oceanisk art som endast var känd från Västergötland, första halvan av 1900-talet.</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>Granskog i ravin.</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Nordvänd skuggig, fuktig lodyta.</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Raul Vicente</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Raul Vicente, Måns Svensson, Ola Hammarström, Robin Isaksson, Martin Westberg, Rikard Anderberg, Maya Edlund</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102650204</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>135830031</v>
+      </c>
+      <c r="B69" t="n">
+        <v>80606</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>264143</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Brittisk torsklav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Peltigera britannica</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Holt.-Hartw. &amp; Tønsberg</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Sundsvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>389640</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7061467</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Återfynd på känd lokal</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Raul Vicente</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135830031</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>102911994</v>
+      </c>
+      <c r="B70" t="n">
+        <v>79497</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6000492</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Protoparmelia ochrococca</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Nyl.) P.M.Jørg. et al.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Sundsvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>389598</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7061433</v>
+      </c>
+      <c r="S70" t="n">
+        <v>25</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Martin Westberg, Raul Vicente, Måns Svensson, Rikard Anderberg, Maya Edlund, Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102911994</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>103566147</v>
+      </c>
+      <c r="B71" t="n">
+        <v>79497</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6000492</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Protoparmelia ochrococca</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Nyl.) P.M.Jørg. et al.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Ravinskog i Sundsvalens nordbrant, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>390019</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7061472</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Maya Edlund, Rikard Anderberg, Martin Westberg, Robin Isaksson, Raul Vicente, Måns Svensson, Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103566147</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>118378110</v>
+      </c>
+      <c r="B72" t="n">
+        <v>79497</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6000492</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Protoparmelia ochrococca</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Nyl.) P.M.Jørg. et al.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Sundsvalens N-sluttning, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>389580</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7061470</v>
+      </c>
+      <c r="S72" t="n">
+        <v>25</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2022-07-25</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2022-07-25</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/118378110</t>
         </is>
@@ -8062,6 +8652,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44517-2023 artfynd.xlsx
+++ b/artfynd/A 44517-2023 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>137002851</v>
       </c>
       <c r="B5" t="n">
-        <v>79557</v>
+        <v>79561</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>137002813</v>
       </c>
       <c r="B9" t="n">
-        <v>78835</v>
+        <v>78839</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
         <v>137002816</v>
       </c>
       <c r="B50" t="n">
-        <v>83463</v>
+        <v>83467</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>137002846</v>
       </c>
       <c r="B58" t="n">
-        <v>83461</v>
+        <v>83465</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 44517-2023 artfynd.xlsx
+++ b/artfynd/A 44517-2023 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>137002851</v>
       </c>
       <c r="B5" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>137002813</v>
       </c>
       <c r="B9" t="n">
-        <v>78839</v>
+        <v>78841</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
         <v>137002816</v>
       </c>
       <c r="B50" t="n">
-        <v>83467</v>
+        <v>83469</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>137002846</v>
       </c>
       <c r="B58" t="n">
-        <v>83465</v>
+        <v>83467</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>137002814</v>
       </c>
       <c r="B62" t="n">
-        <v>78485</v>
+        <v>78487</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 44517-2023 artfynd.xlsx
+++ b/artfynd/A 44517-2023 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>137002851</v>
       </c>
       <c r="B5" t="n">
-        <v>79563</v>
+        <v>79564</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>137002813</v>
       </c>
       <c r="B9" t="n">
-        <v>78841</v>
+        <v>78842</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
         <v>137002816</v>
       </c>
       <c r="B50" t="n">
-        <v>83469</v>
+        <v>83470</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>137002846</v>
       </c>
       <c r="B58" t="n">
-        <v>83467</v>
+        <v>83468</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>137002814</v>
       </c>
       <c r="B62" t="n">
-        <v>78487</v>
+        <v>78488</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 44517-2023 artfynd.xlsx
+++ b/artfynd/A 44517-2023 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>137002851</v>
       </c>
       <c r="B5" t="n">
-        <v>79564</v>
+        <v>79566</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>137002813</v>
       </c>
       <c r="B9" t="n">
-        <v>78842</v>
+        <v>78844</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
         <v>137002816</v>
       </c>
       <c r="B50" t="n">
-        <v>83470</v>
+        <v>83474</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>137002846</v>
       </c>
       <c r="B58" t="n">
-        <v>83468</v>
+        <v>83472</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>137002814</v>
       </c>
       <c r="B62" t="n">
-        <v>78488</v>
+        <v>78490</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 44517-2023 artfynd.xlsx
+++ b/artfynd/A 44517-2023 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>137002851</v>
       </c>
       <c r="B5" t="n">
-        <v>79566</v>
+        <v>79569</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>137002813</v>
       </c>
       <c r="B9" t="n">
-        <v>78844</v>
+        <v>78847</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
         <v>137002816</v>
       </c>
       <c r="B50" t="n">
-        <v>83474</v>
+        <v>83476</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>137002846</v>
       </c>
       <c r="B58" t="n">
-        <v>83472</v>
+        <v>83474</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>137002814</v>
       </c>
       <c r="B62" t="n">
-        <v>78490</v>
+        <v>78493</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 44517-2023 artfynd.xlsx
+++ b/artfynd/A 44517-2023 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>137002851</v>
       </c>
       <c r="B5" t="n">
-        <v>79569</v>
+        <v>79582</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>137002813</v>
       </c>
       <c r="B9" t="n">
-        <v>78847</v>
+        <v>78860</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
         <v>137002816</v>
       </c>
       <c r="B50" t="n">
-        <v>83476</v>
+        <v>83489</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>137002846</v>
       </c>
       <c r="B58" t="n">
-        <v>83474</v>
+        <v>83487</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>137002814</v>
       </c>
       <c r="B62" t="n">
-        <v>78493</v>
+        <v>78506</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 44517-2023 artfynd.xlsx
+++ b/artfynd/A 44517-2023 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>137002851</v>
       </c>
       <c r="B5" t="n">
-        <v>79582</v>
+        <v>79584</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>137002813</v>
       </c>
       <c r="B9" t="n">
-        <v>78860</v>
+        <v>78862</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
         <v>137002816</v>
       </c>
       <c r="B50" t="n">
-        <v>83489</v>
+        <v>83491</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>137002846</v>
       </c>
       <c r="B58" t="n">
-        <v>83487</v>
+        <v>83489</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>137002814</v>
       </c>
       <c r="B62" t="n">
-        <v>78506</v>
+        <v>78508</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 44517-2023 artfynd.xlsx
+++ b/artfynd/A 44517-2023 artfynd.xlsx
@@ -5983,7 +5983,7 @@
         <v>137002816</v>
       </c>
       <c r="B50" t="n">
-        <v>83491</v>
+        <v>83494</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>137002846</v>
       </c>
       <c r="B58" t="n">
-        <v>83489</v>
+        <v>83492</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 44517-2023 artfynd.xlsx
+++ b/artfynd/A 44517-2023 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>137002851</v>
       </c>
       <c r="B5" t="n">
-        <v>79584</v>
+        <v>79594</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>137002813</v>
       </c>
       <c r="B9" t="n">
-        <v>78862</v>
+        <v>78872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
         <v>137002816</v>
       </c>
       <c r="B50" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>137002846</v>
       </c>
       <c r="B58" t="n">
-        <v>83492</v>
+        <v>83502</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>137002814</v>
       </c>
       <c r="B62" t="n">
-        <v>78508</v>
+        <v>78518</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 44517-2023 artfynd.xlsx
+++ b/artfynd/A 44517-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ72"/>
+  <dimension ref="A1:AZ74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135830027</v>
+        <v>137356289</v>
       </c>
       <c r="B6" t="n">
-        <v>83452</v>
+        <v>79594</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1133,37 +1133,48 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>308</v>
+        <v>283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sundsvalen, Jmt</t>
+          <t>Hamborgvallen-Sundsvalen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>390620</v>
+        <v>390809</v>
       </c>
       <c r="R6" t="n">
-        <v>7061569</v>
+        <v>7061617</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1187,22 +1198,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>16:13</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>16:13</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1211,33 +1212,59 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Raul Vicente</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135830027</t>
+          <t>https://artportalen.se/Sighting/137356289</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118378088</v>
+        <v>135830027</v>
       </c>
       <c r="B7" t="n">
-        <v>83302</v>
+        <v>83452</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1245,37 +1272,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Sundsvalen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>389534</v>
+        <v>390620</v>
       </c>
       <c r="R7" t="n">
-        <v>7061458</v>
+        <v>7061569</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1299,12 +1326,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,58 +1352,53 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Cajsa Björkén, Raul Vicente</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378088</t>
+          <t>https://artportalen.se/Sighting/135830027</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118378039</v>
+        <v>118378088</v>
       </c>
       <c r="B8" t="n">
-        <v>83298</v>
+        <v>83302</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>492</v>
+        <v>310</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1376,10 +1408,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>390411</v>
+        <v>389534</v>
       </c>
       <c r="R8" t="n">
-        <v>7061551</v>
+        <v>7061458</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1406,12 +1438,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1425,7 +1457,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>björkhögstubbe</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1442,16 +1474,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378039</t>
+          <t>https://artportalen.se/Sighting/118378088</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137002813</v>
+        <v>118378039</v>
       </c>
       <c r="B9" t="n">
-        <v>78872</v>
+        <v>83298</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,40 +1491,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sundsvalen, Segerdalen, Kall, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>390677</v>
+        <v>390411</v>
       </c>
       <c r="R9" t="n">
-        <v>7061698</v>
+        <v>7061551</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1516,12 +1545,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1530,93 +1559,76 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>björkhögstubbe</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Raul Vicente</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Raul Vicente, Ola Hammarström</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137002813</t>
+          <t>https://artportalen.se/Sighting/118378039</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>101624404</v>
+        <v>137002813</v>
       </c>
       <c r="B10" t="n">
-        <v>96705</v>
+        <v>78872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>535</v>
+        <v>498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skuggmossa</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dicranodontium denudatum</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brid.) E.Britton</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sundsvalen, ravin vid nordsidan., Jmt</t>
+          <t>Sundsvalen, Segerdalen, Kall, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>389605</v>
+        <v>390677</v>
       </c>
       <c r="R10" t="n">
-        <v>7061466</v>
+        <v>7061698</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1643,12 +1655,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1663,73 +1675,87 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Bäckravin med granskog.</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bergvägg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Raul Vicente</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Leif Appelgren, Fredrik Larsson</t>
+          <t>Raul Vicente, Ola Hammarström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101624404</t>
+          <t>https://artportalen.se/Sighting/137002813</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103566149</v>
+        <v>101624404</v>
       </c>
       <c r="B11" t="n">
-        <v>81013</v>
+        <v>96705</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>735</v>
+        <v>535</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skuggkraterlav</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gyalecta friesii</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Flot. ex Körb.</t>
+          <t>(Brid.) E.Britton</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ravinskog i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalen, ravin vid nordsidan., Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>390608</v>
+        <v>389605</v>
       </c>
       <c r="R11" t="n">
-        <v>7061565</v>
+        <v>7061466</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1756,12 +1782,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,35 +1796,41 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Bäckravin med granskog.</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Rothåla gran</t>
+          <t>Bergvägg.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Maya Edlund, Rikard Anderberg, Martin Westberg, Robin Isaksson, Raul Vicente, Måns Svensson, Ola Hammarström</t>
+          <t>Leif Appelgren, Fredrik Larsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566149</t>
+          <t>https://artportalen.se/Sighting/101624404</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103566189</v>
+        <v>103566149</v>
       </c>
       <c r="B12" t="n">
         <v>81013</v>
@@ -1829,14 +1861,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
+          <t>Ravinskog i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>389379</v>
+        <v>390608</v>
       </c>
       <c r="R12" t="n">
-        <v>7061454</v>
+        <v>7061565</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1863,12 +1895,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1893,19 +1925,19 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
+          <t>Maya Edlund, Rikard Anderberg, Martin Westberg, Robin Isaksson, Raul Vicente, Måns Svensson, Ola Hammarström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566189</t>
+          <t>https://artportalen.se/Sighting/103566149</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118378021</v>
+        <v>103566189</v>
       </c>
       <c r="B13" t="n">
         <v>81013</v>
@@ -1936,17 +1968,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>389551</v>
+        <v>389379</v>
       </c>
       <c r="R13" t="n">
-        <v>7061475</v>
+        <v>7061454</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1970,12 +2002,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1989,30 +2021,30 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>granbas</t>
+          <t>Rothåla gran</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378021</t>
+          <t>https://artportalen.se/Sighting/103566189</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118378108</v>
+        <v>118378021</v>
       </c>
       <c r="B14" t="n">
         <v>81013</v>
@@ -2047,10 +2079,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>389432</v>
+        <v>389551</v>
       </c>
       <c r="R14" t="n">
-        <v>7061449</v>
+        <v>7061475</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2077,12 +2109,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2093,6 +2125,11 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>granbas</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2108,16 +2145,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378108</t>
+          <t>https://artportalen.se/Sighting/118378021</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135830026</v>
+        <v>118378108</v>
       </c>
       <c r="B15" t="n">
-        <v>81158</v>
+        <v>81013</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2145,17 +2182,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sundsvalen, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>390620</v>
+        <v>389432</v>
       </c>
       <c r="R15" t="n">
-        <v>7061569</v>
+        <v>7061449</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2179,22 +2216,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>16:13</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>16:13</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2209,27 +2236,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Raul Vicente</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135830026</t>
+          <t>https://artportalen.se/Sighting/118378108</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135830028</v>
+        <v>135830026</v>
       </c>
       <c r="B16" t="n">
-        <v>81157</v>
+        <v>81158</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2261,13 +2288,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>390604</v>
+        <v>390620</v>
       </c>
       <c r="R16" t="n">
-        <v>7061567</v>
+        <v>7061569</v>
       </c>
       <c r="S16" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2296,7 +2323,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2306,7 +2333,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2332,16 +2359,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135830028</t>
+          <t>https://artportalen.se/Sighting/135830026</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>102571913</v>
+        <v>135830028</v>
       </c>
       <c r="B17" t="n">
-        <v>92721</v>
+        <v>81157</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2349,40 +2376,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>918</v>
+        <v>735</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Skuggkraterlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Gyalecta friesii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>Flot. ex Körb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sundsvalen N, Nynäsbäcken O, Jmt</t>
+          <t>Sundsvalen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>389580</v>
+        <v>390604</v>
       </c>
       <c r="R17" t="n">
-        <v>7061470</v>
+        <v>7061567</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2406,12 +2430,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2420,92 +2454,74 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Rikard Anderberg, Maya Edlund, Raul Vicente, Ola Hammarström, Martin Westberg, Robin Isaksson</t>
+          <t>Cajsa Björkén, Raul Vicente</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102571913</t>
+          <t>https://artportalen.se/Sighting/135830028</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>103566174</v>
+        <v>102571913</v>
       </c>
       <c r="B18" t="n">
-        <v>81312</v>
+        <v>92721</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1049</v>
+        <v>918</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalen N, Nynäsbäcken O, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>389653</v>
+        <v>389580</v>
       </c>
       <c r="R18" t="n">
-        <v>7061468</v>
+        <v>7061470</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2529,12 +2545,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2543,35 +2559,51 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Ved i rothåla , rönn?</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
+          <t>Rikard Anderberg, Maya Edlund, Raul Vicente, Ola Hammarström, Martin Westberg, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566174</t>
+          <t>https://artportalen.se/Sighting/102571913</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>103566182</v>
+        <v>103566174</v>
       </c>
       <c r="B19" t="n">
         <v>81312</v>
@@ -2606,10 +2638,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>389508</v>
+        <v>389653</v>
       </c>
       <c r="R19" t="n">
-        <v>7061484</v>
+        <v>7061468</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2655,7 +2687,7 @@
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Rothåla gran</t>
+          <t>Ved i rothåla , rönn?</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2672,16 +2704,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566182</t>
+          <t>https://artportalen.se/Sighting/103566174</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>102911996</v>
+        <v>103566182</v>
       </c>
       <c r="B20" t="n">
-        <v>91905</v>
+        <v>81312</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2689,40 +2721,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>1049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sundsvalen, Jmt</t>
+          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>389598</v>
+        <v>389508</v>
       </c>
       <c r="R20" t="n">
-        <v>7061433</v>
+        <v>7061484</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2746,12 +2775,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2760,56 +2789,60 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Rothåla gran</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Robin Isaksson</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Martin Westberg, Raul Vicente, Måns Svensson, Maya Edlund, Ola Hammarström</t>
+          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102911996</t>
+          <t>https://artportalen.se/Sighting/103566182</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>102911954</v>
+        <v>102911996</v>
       </c>
       <c r="B21" t="n">
-        <v>91923</v>
+        <v>91905</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2822,10 +2855,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>390406</v>
+        <v>389598</v>
       </c>
       <c r="R21" t="n">
-        <v>7061546</v>
+        <v>7061433</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2878,19 +2911,19 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Maya Edlund, Rikard Anderberg, Måns Svensson, Raul Vicente, Martin Westberg, Robin Isaksson</t>
+          <t>Robin Isaksson, Martin Westberg, Raul Vicente, Måns Svensson, Maya Edlund, Ola Hammarström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102911954</t>
+          <t>https://artportalen.se/Sighting/102911996</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118378107</v>
+        <v>102911954</v>
       </c>
       <c r="B22" t="n">
         <v>91923</v>
@@ -2919,16 +2952,19 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Sundsvalen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>389435</v>
+        <v>390406</v>
       </c>
       <c r="R22" t="n">
-        <v>7061405</v>
+        <v>7061546</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2955,12 +2991,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2969,38 +3005,34 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Robin Isaksson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Ola Hammarström, Maya Edlund, Rikard Anderberg, Måns Svensson, Raul Vicente, Martin Westberg, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378107</t>
+          <t>https://artportalen.se/Sighting/102911954</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>102571916</v>
+        <v>118378107</v>
       </c>
       <c r="B23" t="n">
-        <v>79486</v>
+        <v>91923</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3008,37 +3040,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1249</v>
+        <v>1204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sundsvalen N, Nynäsbäcken O, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>389580</v>
+        <v>389435</v>
       </c>
       <c r="R23" t="n">
-        <v>7061470</v>
+        <v>7061405</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3065,12 +3094,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3079,51 +3108,35 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Rikard Anderberg, Maya Edlund, Raul Vicente, Ola Hammarström, Martin Westberg, Robin Isaksson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102571916</t>
+          <t>https://artportalen.se/Sighting/118378107</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>103566191</v>
+        <v>102571916</v>
       </c>
       <c r="B24" t="n">
         <v>79486</v>
@@ -3152,19 +3165,22 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalen N, Nynäsbäcken O, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>389472</v>
+        <v>389580</v>
       </c>
       <c r="R24" t="n">
-        <v>7061433</v>
+        <v>7061470</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3188,12 +3204,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3202,38 +3218,54 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
+          <t>Rikard Anderberg, Maya Edlund, Raul Vicente, Ola Hammarström, Martin Westberg, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566191</t>
+          <t>https://artportalen.se/Sighting/102571916</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118378032</v>
+        <v>103566191</v>
       </c>
       <c r="B25" t="n">
-        <v>75413</v>
+        <v>79486</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3241,37 +3273,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1461</v>
+        <v>1249</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brun skärelav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Schismatomma umbrinum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Coppins &amp; P.James) P.M.Jørg. &amp; Tønsberg</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>390053</v>
+        <v>389472</v>
       </c>
       <c r="R25" t="n">
-        <v>7061464</v>
+        <v>7061433</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3295,12 +3327,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3314,33 +3346,33 @@
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>lodyta</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378032</t>
+          <t>https://artportalen.se/Sighting/103566191</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118378085</v>
+        <v>137356175</v>
       </c>
       <c r="B26" t="n">
-        <v>75413</v>
+        <v>79672</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3348,37 +3380,48 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1461</v>
+        <v>1249</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brun skärelav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Schismatomma umbrinum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Coppins &amp; P.James) P.M.Jørg. &amp; Tønsberg</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Hamborgvallen-Sundsvalen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>389631</v>
+        <v>390823</v>
       </c>
       <c r="R26" t="n">
-        <v>7061464</v>
+        <v>7061639</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3402,12 +3445,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3416,81 +3459,72 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>lodyta</t>
-        </is>
-      </c>
-      <c r="AP26" t="inlineStr">
-        <is>
-          <t>Uppsala-Evolutionsmuseet</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378085</t>
+          <t>https://artportalen.se/Sighting/137356175</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>103566181</v>
+        <v>118378032</v>
       </c>
       <c r="B27" t="n">
-        <v>83312</v>
+        <v>75413</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1467</v>
+        <v>1461</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Brun skärelav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Schismatomma umbrinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Coppins &amp; P.James) P.M.Jørg. &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>389508</v>
+        <v>390053</v>
       </c>
       <c r="R27" t="n">
-        <v>7061484</v>
+        <v>7061464</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3514,12 +3548,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3533,71 +3567,71 @@
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Rothåla gran</t>
+          <t>lodyta</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566181</t>
+          <t>https://artportalen.se/Sighting/118378032</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>103566194</v>
+        <v>118378085</v>
       </c>
       <c r="B28" t="n">
-        <v>83312</v>
+        <v>75413</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1467</v>
+        <v>1461</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Brun skärelav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Schismatomma umbrinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Coppins &amp; P.James) P.M.Jørg. &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>389472</v>
+        <v>389631</v>
       </c>
       <c r="R28" t="n">
-        <v>7061433</v>
+        <v>7061464</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3640,30 +3674,35 @@
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>lodyta</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>Uppsala-Evolutionsmuseet</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566194</t>
+          <t>https://artportalen.se/Sighting/118378085</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118378034</v>
+        <v>103566181</v>
       </c>
       <c r="B29" t="n">
         <v>83312</v>
@@ -3694,17 +3733,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>390082</v>
+        <v>389508</v>
       </c>
       <c r="R29" t="n">
-        <v>7061482</v>
+        <v>7061484</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3728,12 +3767,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3747,33 +3786,33 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>granbas</t>
+          <t>Rothåla gran</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378034</t>
+          <t>https://artportalen.se/Sighting/103566181</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135830030</v>
+        <v>103566194</v>
       </c>
       <c r="B30" t="n">
-        <v>83465</v>
+        <v>83312</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3801,17 +3840,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sundsvalen, Jmt</t>
+          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>390604</v>
+        <v>389472</v>
       </c>
       <c r="R30" t="n">
-        <v>7061561</v>
+        <v>7061433</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3835,22 +3874,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>16:32</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>16:32</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3861,69 +3890,74 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Raul Vicente</t>
+          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135830030</t>
+          <t>https://artportalen.se/Sighting/103566194</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>103566148</v>
+        <v>118378034</v>
       </c>
       <c r="B31" t="n">
-        <v>83315</v>
+        <v>83312</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Liten blekspik</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sclerophora peronella</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ravinskog i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>390101</v>
+        <v>390082</v>
       </c>
       <c r="R31" t="n">
         <v>7061482</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3966,71 +4000,71 @@
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Björkhögstubbe</t>
+          <t>granbas</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Maya Edlund, Rikard Anderberg, Martin Westberg, Robin Isaksson, Raul Vicente, Måns Svensson, Ola Hammarström</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566148</t>
+          <t>https://artportalen.se/Sighting/118378034</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>103566176</v>
+        <v>135830030</v>
       </c>
       <c r="B32" t="n">
-        <v>83315</v>
+        <v>83465</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Liten blekspik</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sclerophora peronella</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>389653</v>
+        <v>390604</v>
       </c>
       <c r="R32" t="n">
-        <v>7061468</v>
+        <v>7061561</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4054,12 +4088,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4070,33 +4114,28 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Rönn</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
+          <t>Cajsa Björkén, Raul Vicente</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566176</t>
+          <t>https://artportalen.se/Sighting/135830030</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>115808940</v>
+        <v>103566148</v>
       </c>
       <c r="B33" t="n">
         <v>83315</v>
@@ -4125,19 +4164,16 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sundsvalens nordsluttning, Jmt</t>
+          <t>Ravinskog i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>389685</v>
+        <v>390101</v>
       </c>
       <c r="R33" t="n">
-        <v>7061500</v>
+        <v>7061482</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4164,17 +4200,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4183,36 +4214,35 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
-      <c r="AP33" t="inlineStr">
-        <is>
-          <t>Uppsala-Evolutionsmuseet</t>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Björkhögstubbe</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Maya Edlund, Rikard Anderberg, Martin Westberg, Robin Isaksson, Raul Vicente, Måns Svensson, Ola Hammarström</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115808940</t>
+          <t>https://artportalen.se/Sighting/103566148</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118378042</v>
+        <v>103566176</v>
       </c>
       <c r="B34" t="n">
         <v>83315</v>
@@ -4243,17 +4273,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>390411</v>
+        <v>389653</v>
       </c>
       <c r="R34" t="n">
-        <v>7061551</v>
+        <v>7061468</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4277,12 +4307,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4296,33 +4326,33 @@
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>björkhögstubbe</t>
+          <t>Rönn</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378042</t>
+          <t>https://artportalen.se/Sighting/103566176</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>102911949</v>
+        <v>115808940</v>
       </c>
       <c r="B35" t="n">
-        <v>75421</v>
+        <v>83315</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4330,21 +4360,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1776</v>
+        <v>1469</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Liten blekspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Sclerophora peronella</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4353,17 +4383,17 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sundsvalen, Jmt</t>
+          <t>Sundsvalens nordsluttning, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>390406</v>
+        <v>389685</v>
       </c>
       <c r="R35" t="n">
-        <v>7061546</v>
+        <v>7061500</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4387,12 +4417,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4405,45 +4440,35 @@
       <c r="AG35" t="b">
         <v>0</v>
       </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AP35" t="inlineStr">
+        <is>
+          <t>Uppsala-Evolutionsmuseet</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Robin Isaksson</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Maya Edlund, Rikard Anderberg, Måns Svensson, Raul Vicente, Martin Westberg, Robin Isaksson</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102911949</t>
+          <t>https://artportalen.se/Sighting/115808940</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>103566178</v>
+        <v>118378042</v>
       </c>
       <c r="B36" t="n">
-        <v>75421</v>
+        <v>83315</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4451,37 +4476,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1776</v>
+        <v>1469</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Liten blekspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Sclerophora peronella</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>389508</v>
+        <v>390411</v>
       </c>
       <c r="R36" t="n">
-        <v>7061484</v>
+        <v>7061551</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4505,12 +4530,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4524,30 +4549,30 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Grangren</t>
+          <t>björkhögstubbe</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566178</t>
+          <t>https://artportalen.se/Sighting/118378042</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>106652352</v>
+        <v>102911949</v>
       </c>
       <c r="B37" t="n">
         <v>75421</v>
@@ -4581,14 +4606,14 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sundsvalen, Jormlien, Frostviken, Jmt</t>
+          <t>Sundsvalen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>389539</v>
+        <v>390406</v>
       </c>
       <c r="R37" t="n">
-        <v>7061476</v>
+        <v>7061546</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4615,12 +4640,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4629,40 +4654,46 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>Oceanisk grannaturskog.</t>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Raul Vicente</t>
+          <t>Robin Isaksson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Raul Vicente</t>
+          <t>Ola Hammarström, Maya Edlund, Rikard Anderberg, Måns Svensson, Raul Vicente, Martin Westberg, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106652352</t>
+          <t>https://artportalen.se/Sighting/102911949</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118378020</v>
+        <v>103566178</v>
       </c>
       <c r="B38" t="n">
         <v>75421</v>
@@ -4693,17 +4724,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>389551</v>
+        <v>389508</v>
       </c>
       <c r="R38" t="n">
-        <v>7061475</v>
+        <v>7061484</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4727,12 +4758,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4746,68 +4777,71 @@
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>granbas</t>
+          <t>Grangren</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378020</t>
+          <t>https://artportalen.se/Sighting/103566178</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118378115</v>
+        <v>106652352</v>
       </c>
       <c r="B39" t="n">
-        <v>80433</v>
+        <v>75421</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>1776</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Sundsvalen, Jormlien, Frostviken, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>389580</v>
+        <v>389539</v>
       </c>
       <c r="R39" t="n">
-        <v>7061470</v>
+        <v>7061476</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4848,76 +4882,81 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>rönn</t>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Oceanisk grannaturskog.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Raul Vicente</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Raul Vicente</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378115</t>
+          <t>https://artportalen.se/Sighting/106652352</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135830025</v>
+        <v>118378020</v>
       </c>
       <c r="B40" t="n">
-        <v>98000</v>
+        <v>75421</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2389</v>
+        <v>1776</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Purpurmylia</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Mylia taylorii</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hook.) Gray</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sundsvalen, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>390836</v>
+        <v>389551</v>
       </c>
       <c r="R40" t="n">
-        <v>7061634</v>
+        <v>7061475</v>
       </c>
       <c r="S40" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4941,22 +4980,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>16:08</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>16:08</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4967,74 +4996,71 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>granbas</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Raul Vicente</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135830025</t>
+          <t>https://artportalen.se/Sighting/118378020</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>102583100</v>
+        <v>118378115</v>
       </c>
       <c r="B41" t="n">
-        <v>96350</v>
+        <v>80433</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2813</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>utan kapsel</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sundsvalen N, O Nynäsbäcken, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>389560</v>
+        <v>389580</v>
       </c>
       <c r="R41" t="n">
-        <v>7061465</v>
+        <v>7061470</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5061,12 +5087,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5075,44 +5101,38 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>ravin</t>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Rikard Anderberg, Maya Edlund</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102583100</t>
+          <t>https://artportalen.se/Sighting/118378115</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>101624453</v>
+        <v>135830025</v>
       </c>
       <c r="B42" t="n">
-        <v>96459</v>
+        <v>98000</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5120,41 +5140,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2819</v>
+        <v>2389</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trind spretmossa</t>
+          <t>Purpurmylia</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Herzogiella striatella</t>
+          <t>Mylia taylorii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hook.) Gray</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sundsvalen, ravin vid nordsidan., Jmt</t>
+          <t>Sundsvalen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>389605</v>
+        <v>390836</v>
       </c>
       <c r="R42" t="n">
-        <v>7061466</v>
+        <v>7061634</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5178,12 +5194,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5192,44 +5218,33 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Bäckravin med granskog.</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Bergvägg.</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Leif Appelgren, Fredrik Larsson</t>
+          <t>Cajsa Björkén, Raul Vicente</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101624453</t>
+          <t>https://artportalen.se/Sighting/135830025</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>101775139</v>
+        <v>102583100</v>
       </c>
       <c r="B43" t="n">
-        <v>96459</v>
+        <v>96350</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5237,34 +5252,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2819</v>
+        <v>2813</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Trind spretmossa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Herzogiella striatella</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>utan kapsel</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sundsvalen, norra sluttningen, Jmt</t>
+          <t>Sundsvalen N, O Nynäsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>389642</v>
+        <v>389560</v>
       </c>
       <c r="R43" t="n">
-        <v>7061462</v>
+        <v>7061465</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5291,17 +5314,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Projektet Northern hepatic mat</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5310,71 +5328,86 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>ravin</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Tomas Hallingbäck</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Tomas Hallingbäck, Fredrik Larsson, Karin Wiklund, Leif Appelgren, Anna Pielach</t>
+          <t>Rikard Anderberg, Maya Edlund</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101775139</t>
+          <t>https://artportalen.se/Sighting/102583100</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118378106</v>
+        <v>101624453</v>
       </c>
       <c r="B44" t="n">
-        <v>79327</v>
+        <v>96459</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>2819</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trind spretmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Herzogiella striatella</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Sundsvalen, ravin vid nordsidan., Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>389412</v>
+        <v>389605</v>
       </c>
       <c r="R44" t="n">
-        <v>7061456</v>
+        <v>7061466</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5398,12 +5431,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5412,38 +5445,44 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Bäckravin med granskog.</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>Bergvägg.</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Leif Appelgren, Fredrik Larsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378106</t>
+          <t>https://artportalen.se/Sighting/101624453</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>103566195</v>
+        <v>101775139</v>
       </c>
       <c r="B45" t="n">
-        <v>75300</v>
+        <v>96459</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5451,37 +5490,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6428</v>
+        <v>2819</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Trind spretmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Herzogiella striatella</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalen, norra sluttningen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>389472</v>
+        <v>389642</v>
       </c>
       <c r="R45" t="n">
-        <v>7061433</v>
+        <v>7061462</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5505,12 +5544,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Projektet Northern hepatic mat</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5521,58 +5565,53 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Tomas Hallingbäck</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
+          <t>Tomas Hallingbäck, Fredrik Larsson, Karin Wiklund, Leif Appelgren, Anna Pielach</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566195</t>
+          <t>https://artportalen.se/Sighting/101775139</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118378022</v>
+        <v>118378106</v>
       </c>
       <c r="B46" t="n">
-        <v>75300</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5582,10 +5621,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>389551</v>
+        <v>389412</v>
       </c>
       <c r="R46" t="n">
-        <v>7061475</v>
+        <v>7061456</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5612,12 +5651,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5631,7 +5670,7 @@
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>granbas</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5648,16 +5687,16 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378022</t>
+          <t>https://artportalen.se/Sighting/118378106</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>103566197</v>
+        <v>103566195</v>
       </c>
       <c r="B47" t="n">
-        <v>83290</v>
+        <v>75300</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5665,21 +5704,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6439</v>
+        <v>6428</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5755,16 +5794,16 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566197</t>
+          <t>https://artportalen.se/Sighting/103566195</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118378040</v>
+        <v>118378022</v>
       </c>
       <c r="B48" t="n">
-        <v>83290</v>
+        <v>75300</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5772,21 +5811,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6439</v>
+        <v>6428</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5796,10 +5835,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>390411</v>
+        <v>389551</v>
       </c>
       <c r="R48" t="n">
-        <v>7061551</v>
+        <v>7061475</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5845,7 +5884,7 @@
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>björkhögstubbe</t>
+          <t>granbas</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5862,54 +5901,54 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378040</t>
+          <t>https://artportalen.se/Sighting/118378022</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118378027</v>
+        <v>103566197</v>
       </c>
       <c r="B49" t="n">
-        <v>83307</v>
+        <v>83290</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6440</v>
+        <v>6439</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>389582</v>
+        <v>389472</v>
       </c>
       <c r="R49" t="n">
-        <v>7061446</v>
+        <v>7061433</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5933,17 +5972,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5957,74 +5991,71 @@
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378027</t>
+          <t>https://artportalen.se/Sighting/103566197</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>137002816</v>
+        <v>118378040</v>
       </c>
       <c r="B50" t="n">
-        <v>83504</v>
+        <v>83290</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>6439</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sundsvalen, Segerdalen, Kall, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>390677</v>
+        <v>390411</v>
       </c>
       <c r="R50" t="n">
-        <v>7061698</v>
+        <v>7061551</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6048,12 +6079,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6062,54 +6093,38 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>björkhögstubbe</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Raul Vicente</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Raul Vicente, Ola Hammarström</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137002816</t>
+          <t>https://artportalen.se/Sighting/118378040</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118378086</v>
+        <v>118378027</v>
       </c>
       <c r="B51" t="n">
-        <v>79413</v>
+        <v>83307</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6117,21 +6132,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6450</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6141,10 +6156,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>389615</v>
+        <v>389582</v>
       </c>
       <c r="R51" t="n">
-        <v>7061456</v>
+        <v>7061446</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6171,12 +6186,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6190,7 +6210,7 @@
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6207,16 +6227,16 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378086</t>
+          <t>https://artportalen.se/Sighting/118378027</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118378113</v>
+        <v>137002816</v>
       </c>
       <c r="B52" t="n">
-        <v>80432</v>
+        <v>83504</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6224,37 +6244,40 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Sundsvalen, Segerdalen, Kall, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>389580</v>
+        <v>390677</v>
       </c>
       <c r="R52" t="n">
-        <v>7061470</v>
+        <v>7061698</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6278,12 +6301,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6292,76 +6315,92 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Raul Vicente</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Raul Vicente, Ola Hammarström</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378113</t>
+          <t>https://artportalen.se/Sighting/137002816</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135830023</v>
+        <v>118378086</v>
       </c>
       <c r="B53" t="n">
-        <v>79729</v>
+        <v>79413</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6459</v>
+        <v>6450</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Sundsvalen, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>390836</v>
+        <v>389615</v>
       </c>
       <c r="R53" t="n">
-        <v>7061634</v>
+        <v>7061456</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6385,22 +6424,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6411,69 +6440,71 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>block</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Raul Vicente</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135830023</t>
+          <t>https://artportalen.se/Sighting/118378086</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>103432381</v>
+        <v>118378113</v>
       </c>
       <c r="B54" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sundsvalen, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>390528</v>
+        <v>389580</v>
       </c>
       <c r="R54" t="n">
-        <v>7061549</v>
+        <v>7061470</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6500,12 +6531,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2022-07-24</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2022-07-24</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6514,38 +6545,38 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Robin Isaksson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Martin Westberg</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103432381</t>
+          <t>https://artportalen.se/Sighting/118378113</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118378112</v>
+        <v>135830023</v>
       </c>
       <c r="B55" t="n">
-        <v>80468</v>
+        <v>79729</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6553,37 +6584,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6464</v>
+        <v>6459</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Sundsvalen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>389580</v>
+        <v>390836</v>
       </c>
       <c r="R55" t="n">
-        <v>7061470</v>
+        <v>7061634</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6607,12 +6638,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6623,74 +6664,72 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Cajsa Björkén, Raul Vicente</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378112</t>
+          <t>https://artportalen.se/Sighting/135830023</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>103566180</v>
+        <v>103432381</v>
       </c>
       <c r="B56" t="n">
-        <v>83305</v>
+        <v>80461</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6486</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalen, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>389508</v>
+        <v>390528</v>
       </c>
       <c r="R56" t="n">
-        <v>7061484</v>
+        <v>7061549</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6714,12 +6753,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-24</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-24</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6728,60 +6767,60 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Rothåla gran</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Robin Isaksson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
+          <t>Robin Isaksson, Martin Westberg</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566180</t>
+          <t>https://artportalen.se/Sighting/103432381</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118378024</v>
+        <v>118378112</v>
       </c>
       <c r="B57" t="n">
-        <v>83305</v>
+        <v>80468</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6486</v>
+        <v>6464</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6791,10 +6830,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>389551</v>
+        <v>389580</v>
       </c>
       <c r="R57" t="n">
-        <v>7061475</v>
+        <v>7061470</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6821,12 +6860,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6840,7 +6879,7 @@
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>granbas</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -6857,16 +6896,16 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378024</t>
+          <t>https://artportalen.se/Sighting/118378112</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>137002846</v>
+        <v>103566180</v>
       </c>
       <c r="B58" t="n">
-        <v>83502</v>
+        <v>83305</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6892,22 +6931,19 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sundsvalen, Segerdalen, Kall, Jmt</t>
+          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>390777</v>
+        <v>389508</v>
       </c>
       <c r="R58" t="n">
-        <v>7061697</v>
+        <v>7061484</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6931,12 +6967,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6945,56 +6981,60 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Rothåla gran</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Raul Vicente</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Raul Vicente, Ola Hammarström</t>
+          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137002846</t>
+          <t>https://artportalen.se/Sighting/103566180</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118378045</v>
+        <v>118378024</v>
       </c>
       <c r="B59" t="n">
-        <v>78333</v>
+        <v>83305</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228575</v>
+        <v>6486</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Brun svartspik</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenothecopsis epithallina</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7004,10 +7044,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>390743</v>
+        <v>389551</v>
       </c>
       <c r="R59" t="n">
-        <v>7061546</v>
+        <v>7061475</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7053,12 +7093,7 @@
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>på Chaenotheca på grov gran</t>
-        </is>
-      </c>
-      <c r="AP59" t="inlineStr">
-        <is>
-          <t>Uppsala-Evolutionsmuseet</t>
+          <t>granbas</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7075,54 +7110,57 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378045</t>
+          <t>https://artportalen.se/Sighting/118378024</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>103566184</v>
+        <v>137002846</v>
       </c>
       <c r="B60" t="n">
-        <v>78339</v>
+        <v>83502</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228579</v>
+        <v>6486</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalen, Segerdalen, Kall, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>389508</v>
+        <v>390777</v>
       </c>
       <c r="R60" t="n">
-        <v>7061484</v>
+        <v>7061697</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7146,12 +7184,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7160,38 +7198,34 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Raul Vicente</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
+          <t>Raul Vicente, Ola Hammarström</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566184</t>
+          <t>https://artportalen.se/Sighting/137002846</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118378028</v>
+        <v>118378045</v>
       </c>
       <c r="B61" t="n">
-        <v>78339</v>
+        <v>78333</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7199,16 +7233,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228579</v>
+        <v>228575</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Brun svartspik</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenothecopsis epithallina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7223,10 +7257,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>389582</v>
+        <v>390743</v>
       </c>
       <c r="R61" t="n">
-        <v>7061446</v>
+        <v>7061546</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7261,11 +7295,6 @@
           <t>2022-07-27</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7277,7 +7306,12 @@
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>på Chaenotheca på grov gran</t>
+        </is>
+      </c>
+      <c r="AP61" t="inlineStr">
+        <is>
+          <t>Uppsala-Evolutionsmuseet</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7294,16 +7328,16 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118378028</t>
+          <t>https://artportalen.se/Sighting/118378045</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>137002814</v>
+        <v>103566184</v>
       </c>
       <c r="B62" t="n">
-        <v>78518</v>
+        <v>78339</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7329,19 +7363,16 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sundsvalen, Segerdalen, Kall, Jmt</t>
+          <t>Ravinskog kring Nynäsbäcken i Sundsvalens nordbrant, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>390677</v>
+        <v>389508</v>
       </c>
       <c r="R62" t="n">
-        <v>7061698</v>
+        <v>7061484</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7368,12 +7399,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7382,54 +7413,38 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Raul Vicente</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Raul Vicente, Ola Hammarström</t>
+          <t>Ola Hammarström, Måns Svensson, Raul Vicente, Robin Isaksson, Martin Westberg, Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137002814</t>
+          <t>https://artportalen.se/Sighting/103566184</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>103432374</v>
+        <v>118378028</v>
       </c>
       <c r="B63" t="n">
-        <v>86637</v>
+        <v>78339</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7437,32 +7452,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229848</v>
+        <v>228579</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Refractohilum galligenum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sundsvalen, Jmt</t>
+          <t>Sundsvalens N-sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>390528</v>
+        <v>389582</v>
       </c>
       <c r="R63" t="n">
-        <v>7061549</v>
+        <v>7061446</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7489,12 +7506,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2022-07-24</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2022-07-24</t>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7503,96 +7525,79 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>stuplav</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="AL63" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Nephroma bellum # rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Robin Isaksson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Martin Westberg</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103432374</t>
+          <t>https://artportalen.se/Sighting/118378028</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>101775142</v>
+        <v>137002814</v>
       </c>
       <c r="B64" t="n">
-        <v>97921</v>
+        <v>78518</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>233219</v>
+        <v>228579</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vågig rutlungmossa</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Conocephalum salebrosum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Szweyk., Buczk. &amp; Odrzyk.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sundsvalen, norra sluttningen, Jmt</t>
+          <t>Sundsvalen, Segerdalen, Kall, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>390389</v>
+        <v>390677</v>
       </c>
       <c r="R64" t="n">
-        <v>7061515</v>
+        <v>7061698</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7616,17 +7621,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Projektet Northern hepatic mat</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7635,72 +7635,87 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Tomas Hallingbäck</t>
+          <t>Raul Vicente</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Tomas Hallingbäck, Fredrik Larsson, Karin Wiklund, Leif Appelgren, Anna Pielach</t>
+          <t>Raul Vicente, Ola Hammarström</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101775142</t>
+          <t>https://artportalen.se/Sighting/137002814</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>102583094</v>
+        <v>103432374</v>
       </c>
       <c r="B65" t="n">
-        <v>97921</v>
+        <v>86637</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>233219</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Vågig rutlungmossa</t>
-        </is>
+        <v>229848</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Conocephalum salebrosum</t>
+          <t>Refractohilum galligenum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Szweyk., Buczk. &amp; Odrzyk.</t>
+          <t>D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Sundsvalen N, O Nynäsbäcken, Jmt</t>
+          <t>Sundsvalen, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>389560</v>
+        <v>390528</v>
       </c>
       <c r="R65" t="n">
-        <v>7061465</v>
+        <v>7061549</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7727,12 +7742,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-24</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-24</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7741,71 +7756,80 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>ravin</t>
-        </is>
-      </c>
-      <c r="AQ65" t="inlineStr">
-        <is>
-          <t>Rikard Anderberg</t>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>stuplav</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="AL65" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Nephroma bellum # rönn</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Robin Isaksson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Rikard Anderberg, Maya Edlund</t>
+          <t>Robin Isaksson, Martin Westberg</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102583094</t>
+          <t>https://artportalen.se/Sighting/103432374</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>101775120</v>
+        <v>101775142</v>
       </c>
       <c r="B66" t="n">
-        <v>97450</v>
+        <v>97921</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>233357</v>
+        <v>233219</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lidvitmossa</t>
+          <t>Vågig rutlungmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sphagnum rubiginosum</t>
+          <t>Conocephalum salebrosum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Flatberg</t>
+          <t>Szweyk., Buczk. &amp; Odrzyk.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7815,10 +7839,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>390757</v>
+        <v>390389</v>
       </c>
       <c r="R66" t="n">
-        <v>7061536</v>
+        <v>7061515</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7881,62 +7905,55 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101775120</t>
+          <t>https://artportalen.se/Sighting/101775142</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>102650188</v>
+        <v>102583094</v>
       </c>
       <c r="B67" t="n">
-        <v>80474</v>
+        <v>97921</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>264143</v>
+        <v>233219</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Brittisk torsklav</t>
+          <t>Vågig rutlungmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Peltigera britannica</t>
+          <t>Conocephalum salebrosum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Gyeln.) Holt.-Hartw. &amp; Tønsberg</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Szweyk., Buczk. &amp; Odrzyk.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Sundsvalen, Jmt</t>
+          <t>Sundsvalen N, O Nynäsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>389672</v>
+        <v>389560</v>
       </c>
       <c r="R67" t="n">
-        <v>7061478</v>
+        <v>7061465</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7971,11 +7988,6 @@
           <t>2022-07-27</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Andra moderna lokalen för Sverige.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7986,86 +7998,80 @@
       <c r="AG67" t="b">
         <v>0</v>
       </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Granskog i ravin.</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Nordvänd skuggig, fuktig lodyta.</t>
+          <t>ravin</t>
+        </is>
+      </c>
+      <c r="AQ67" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Raul Vicente</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Raul Vicente, Måns Svensson, Ola Hammarström, Robin Isaksson, Martin Westberg, Rikard Anderberg, Maya Edlund</t>
+          <t>Rikard Anderberg, Maya Edlund</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102650188</t>
+          <t>https://artportalen.se/Sighting/102583094</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>102650204</v>
+        <v>101775120</v>
       </c>
       <c r="B68" t="n">
-        <v>80474</v>
+        <v>97450</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>264143</v>
+        <v>233357</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Brittisk torsklav</t>
+          <t>Lidvitmossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Peltigera britannica</t>
+          <t>Sphagnum rubiginosum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Gyeln.) Holt.-Hartw. &amp; Tønsberg</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+          <t>Flatberg</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Sundsvalen, Jmt</t>
+          <t>Sundsvalen, norra sluttningen, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>389623</v>
+        <v>390757</v>
       </c>
       <c r="R68" t="n">
-        <v>7061457</v>
+        <v>7061536</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8092,17 +8098,17 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Andra moderna lokalen i Sverige. Dellokal 2 i Sundsvalen. Arten är även känd från Skäckerfjällen. Västlig och oceanisk art som endast var känd från Västergötland, första halvan av 1900-talet.</t>
+          <t>Projektet Northern hepatic mat</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8111,44 +8117,33 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>Granskog i ravin.</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Nordvänd skuggig, fuktig lodyta.</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Raul Vicente</t>
+          <t>Tomas Hallingbäck</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Raul Vicente, Måns Svensson, Ola Hammarström, Robin Isaksson, Martin Westberg, Rikard Anderberg, Maya Edlund</t>
+          <t>Tomas Hallingbäck, Fredrik Larsson, Karin Wiklund, Leif Appelgren, Anna Pielach</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102650204</t>
+          <t>https://artportalen.se/Sighting/101775120</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135830031</v>
+        <v>102650188</v>
       </c>
       <c r="B69" t="n">
-        <v>80606</v>
+        <v>80474</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8173,8 +8168,16 @@
           <t>(Gyeln.) Holt.-Hartw. &amp; Tønsberg</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
@@ -8183,13 +8186,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>389640</v>
+        <v>389672</v>
       </c>
       <c r="R69" t="n">
-        <v>7061467</v>
+        <v>7061478</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8213,27 +8216,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>17:16</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>17:16</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Återfynd på känd lokal</t>
+          <t>Andra moderna lokalen för Sverige.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8246,51 +8239,74 @@
       <c r="AG69" t="b">
         <v>0</v>
       </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>Granskog i ravin.</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Nordvänd skuggig, fuktig lodyta.</t>
+        </is>
+      </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Raul Vicente</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Raul Vicente</t>
+          <t>Raul Vicente, Måns Svensson, Ola Hammarström, Robin Isaksson, Martin Westberg, Rikard Anderberg, Maya Edlund</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135830031</t>
+          <t>https://artportalen.se/Sighting/102650188</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>102911994</v>
+        <v>102650204</v>
       </c>
       <c r="B70" t="n">
-        <v>79497</v>
+        <v>80474</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6000492</v>
+        <v>264143</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Brittisk torsklav</t>
+        </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Protoparmelia ochrococca</t>
+          <t>Peltigera britannica</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) P.M.Jørg. et al.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+          <t>(Gyeln.) Holt.-Hartw. &amp; Tønsberg</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
@@ -8299,10 +8315,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>389598</v>
+        <v>389623</v>
       </c>
       <c r="R70" t="n">
-        <v>7061433</v>
+        <v>7061457</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8337,6 +8353,11 @@
           <t>2022-07-27</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Andra moderna lokalen i Sverige. Dellokal 2 i Sundsvalen. Arten är även känd från Skäckerfjällen. Västlig och oceanisk art som endast var känd från Västergötland, första halvan av 1900-talet.</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -8347,75 +8368,78 @@
       <c r="AG70" t="b">
         <v>0</v>
       </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>Granskog i ravin.</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Nordvänd skuggig, fuktig lodyta.</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Robin Isaksson</t>
+          <t>Raul Vicente</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Martin Westberg, Raul Vicente, Måns Svensson, Rikard Anderberg, Maya Edlund, Ola Hammarström</t>
+          <t>Raul Vicente, Måns Svensson, Ola Hammarström, Robin Isaksson, Martin Westberg, Rikard Anderberg, Maya Edlund</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102911994</t>
+          <t>https://artportalen.se/Sighting/102650204</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>103566147</v>
+        <v>135830031</v>
       </c>
       <c r="B71" t="n">
-        <v>79497</v>
+        <v>80606</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6000492</v>
+        <v>264143</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Brittisk torsklav</t>
+        </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Protoparmelia ochrococca</t>
+          <t>Peltigera britannica</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) P.M.Jørg. et al.</t>
+          <t>(Gyeln.) Holt.-Hartw. &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Ravinskog i Sundsvalens nordbrant, Jmt</t>
+          <t>Sundsvalen, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>390019</v>
+        <v>389640</v>
       </c>
       <c r="R71" t="n">
-        <v>7061472</v>
+        <v>7061467</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8442,12 +8466,27 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Återfynd på känd lokal</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8456,35 +8495,31 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Maya Edlund, Rikard Anderberg, Martin Westberg, Robin Isaksson, Raul Vicente, Måns Svensson, Ola Hammarström</t>
+          <t>Cajsa Björkén, Raul Vicente</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566147</t>
+          <t>https://artportalen.se/Sighting/135830031</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118378110</v>
+        <v>102911994</v>
       </c>
       <c r="B72" t="n">
         <v>79497</v>
@@ -8508,16 +8543,19 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Sundsvalens N-sluttning, Jmt</t>
+          <t>Sundsvalen, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>389580</v>
+        <v>389598</v>
       </c>
       <c r="R72" t="n">
-        <v>7061470</v>
+        <v>7061433</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8544,12 +8582,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8558,27 +8596,242 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Robin Isaksson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Robin Isaksson, Martin Westberg, Raul Vicente, Måns Svensson, Rikard Anderberg, Maya Edlund, Ola Hammarström</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102911994</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>103566147</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79497</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6000492</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Protoparmelia ochrococca</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Nyl.) P.M.Jørg. et al.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Ravinskog i Sundsvalens nordbrant, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>390019</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7061472</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Maya Edlund, Rikard Anderberg, Martin Westberg, Robin Isaksson, Raul Vicente, Måns Svensson, Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103566147</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>118378110</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79497</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6000492</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Protoparmelia ochrococca</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Nyl.) P.M.Jørg. et al.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Sundsvalens N-sluttning, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>389580</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7061470</v>
+      </c>
+      <c r="S74" t="n">
+        <v>25</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2022-07-25</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2022-07-25</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/118378110</t>
         </is>
@@ -8657,6 +8910,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44517-2023 artfynd.xlsx
+++ b/artfynd/A 44517-2023 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>137002851</v>
       </c>
       <c r="B5" t="n">
-        <v>79594</v>
+        <v>79597</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>137356289</v>
       </c>
       <c r="B6" t="n">
-        <v>79594</v>
+        <v>79597</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>137002813</v>
       </c>
       <c r="B10" t="n">
-        <v>78872</v>
+        <v>78875</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>137356175</v>
       </c>
       <c r="B26" t="n">
-        <v>79672</v>
+        <v>79675</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>137002816</v>
       </c>
       <c r="B52" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
         <v>137002846</v>
       </c>
       <c r="B60" t="n">
-        <v>83502</v>
+        <v>83505</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>137002814</v>
       </c>
       <c r="B64" t="n">
-        <v>78518</v>
+        <v>78521</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 44517-2023 artfynd.xlsx
+++ b/artfynd/A 44517-2023 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>137002851</v>
       </c>
       <c r="B5" t="n">
-        <v>79597</v>
+        <v>79602</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>137356289</v>
       </c>
       <c r="B6" t="n">
-        <v>79597</v>
+        <v>79602</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>137002813</v>
       </c>
       <c r="B10" t="n">
-        <v>78875</v>
+        <v>78880</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>137356175</v>
       </c>
       <c r="B26" t="n">
-        <v>79675</v>
+        <v>79680</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>137002816</v>
       </c>
       <c r="B52" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
         <v>137002846</v>
       </c>
       <c r="B60" t="n">
-        <v>83505</v>
+        <v>83510</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>137002814</v>
       </c>
       <c r="B64" t="n">
-        <v>78521</v>
+        <v>78526</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 44517-2023 artfynd.xlsx
+++ b/artfynd/A 44517-2023 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>137002851</v>
       </c>
       <c r="B5" t="n">
-        <v>79602</v>
+        <v>79613</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>137356289</v>
       </c>
       <c r="B6" t="n">
-        <v>79602</v>
+        <v>79613</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>137002813</v>
       </c>
       <c r="B10" t="n">
-        <v>78880</v>
+        <v>78891</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>137356175</v>
       </c>
       <c r="B26" t="n">
-        <v>79680</v>
+        <v>79691</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>137002816</v>
       </c>
       <c r="B52" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
         <v>137002846</v>
       </c>
       <c r="B60" t="n">
-        <v>83510</v>
+        <v>83521</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>137002814</v>
       </c>
       <c r="B64" t="n">
-        <v>78526</v>
+        <v>78537</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 44517-2023 artfynd.xlsx
+++ b/artfynd/A 44517-2023 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>137002851</v>
       </c>
       <c r="B5" t="n">
-        <v>79613</v>
+        <v>79614</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>137356289</v>
       </c>
       <c r="B6" t="n">
-        <v>79613</v>
+        <v>79614</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>137002813</v>
       </c>
       <c r="B10" t="n">
-        <v>78891</v>
+        <v>78892</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>137356175</v>
       </c>
       <c r="B26" t="n">
-        <v>79691</v>
+        <v>79692</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>137002816</v>
       </c>
       <c r="B52" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
         <v>137002846</v>
       </c>
       <c r="B60" t="n">
-        <v>83521</v>
+        <v>83522</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>137002814</v>
       </c>
       <c r="B64" t="n">
-        <v>78537</v>
+        <v>78538</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 44517-2023 artfynd.xlsx
+++ b/artfynd/A 44517-2023 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>137002851</v>
       </c>
       <c r="B5" t="n">
-        <v>79614</v>
+        <v>79616</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>137356289</v>
       </c>
       <c r="B6" t="n">
-        <v>79614</v>
+        <v>79616</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>137002813</v>
       </c>
       <c r="B10" t="n">
-        <v>78892</v>
+        <v>78894</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>137356175</v>
       </c>
       <c r="B26" t="n">
-        <v>79692</v>
+        <v>79694</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>137002816</v>
       </c>
       <c r="B52" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
         <v>137002846</v>
       </c>
       <c r="B60" t="n">
-        <v>83522</v>
+        <v>83524</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>137002814</v>
       </c>
       <c r="B64" t="n">
-        <v>78538</v>
+        <v>78540</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 44517-2023 artfynd.xlsx
+++ b/artfynd/A 44517-2023 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>137002851</v>
       </c>
       <c r="B5" t="n">
-        <v>79616</v>
+        <v>79617</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>137002813</v>
       </c>
       <c r="B10" t="n">
-        <v>78894</v>
+        <v>78895</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>137002816</v>
       </c>
       <c r="B52" t="n">
-        <v>83526</v>
+        <v>83527</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
         <v>137002846</v>
       </c>
       <c r="B60" t="n">
-        <v>83524</v>
+        <v>83525</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>137002814</v>
       </c>
       <c r="B64" t="n">
-        <v>78540</v>
+        <v>78541</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 44517-2023 artfynd.xlsx
+++ b/artfynd/A 44517-2023 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>137002851</v>
       </c>
       <c r="B5" t="n">
-        <v>79617</v>
+        <v>79620</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>137356289</v>
       </c>
       <c r="B6" t="n">
-        <v>79616</v>
+        <v>79620</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>137002813</v>
       </c>
       <c r="B10" t="n">
-        <v>78895</v>
+        <v>78898</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>137356175</v>
       </c>
       <c r="B26" t="n">
-        <v>79694</v>
+        <v>79698</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>137002816</v>
       </c>
       <c r="B52" t="n">
-        <v>83527</v>
+        <v>83530</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
         <v>137002846</v>
       </c>
       <c r="B60" t="n">
-        <v>83525</v>
+        <v>83528</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>137002814</v>
       </c>
       <c r="B64" t="n">
-        <v>78541</v>
+        <v>78544</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
